--- a/data/output/sim_gridrnd/ABS1/group_500_20/results/ABS1_G4_results_summary.xlsx
+++ b/data/output/sim_gridrnd/ABS1/group_500_20/results/ABS1_G4_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,384 +466,439 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S03_G4_499_20_ABS1</t>
+          <t>S01_G4_499_22_ABS1</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>499</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>32.61675315048184</v>
       </c>
       <c r="D2" t="n">
-        <v>29.65159377316531</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
         <v>499</v>
@@ -852,244 +907,277 @@
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>507.1435808085691</v>
-      </c>
-      <c r="J2" t="n">
-        <v>18.91805274422854</v>
-      </c>
-      <c r="K2" t="n">
-        <v>505.3529703813916</v>
-      </c>
-      <c r="L2" t="n">
-        <v>14.14254694645346</v>
-      </c>
-      <c r="M2" t="n">
-        <v>497.8323396763439</v>
-      </c>
-      <c r="N2" t="n">
-        <v>21.6347889509723</v>
-      </c>
-      <c r="O2" t="n">
-        <v>498.6095521088272</v>
-      </c>
-      <c r="P2" t="n">
-        <v>23.72010361764607</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>498.5719309545675</v>
-      </c>
       <c r="R2" t="n">
-        <v>22.20798283940995</v>
+        <v>498.4</v>
       </c>
       <c r="S2" t="n">
-        <v>499.074258239746</v>
+        <v>33.47</v>
       </c>
       <c r="T2" t="n">
-        <v>23.96107039565435</v>
+        <v>489.9</v>
       </c>
       <c r="U2" t="n">
-        <v>500.6827444965603</v>
+        <v>30.09</v>
       </c>
       <c r="V2" t="n">
-        <v>24.07528467363065</v>
+        <v>490.28</v>
       </c>
       <c r="W2" t="n">
-        <v>499.4087224054888</v>
+        <v>26.79</v>
       </c>
       <c r="X2" t="n">
-        <v>24.09646085866094</v>
+        <v>494.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>498.110591426145</v>
+        <v>30.71</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.92825833891802</v>
+        <v>496.35</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.5384615384615384</v>
+        <v>28.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.559322033898305</v>
+        <v>499.06</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2307692307692308</v>
+        <v>26.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.08163265306122448</v>
+        <v>501.69</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1016949152542373</v>
+        <v>24.27</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1159420289855072</v>
+        <v>502.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.1392405063291139</v>
+        <v>24.7</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0898876404494382</v>
+        <v>500.03</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0505050505050505</v>
+        <v>24.73</v>
       </c>
       <c r="AJ2" t="n">
-        <v>508.325</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>511.75</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>504.2875</v>
+        <v>0.05</v>
       </c>
       <c r="AM2" t="n">
-        <v>500.48</v>
+        <v>0.02</v>
       </c>
       <c r="AN2" t="n">
-        <v>500.7</v>
+        <v>0.01666666666666667</v>
       </c>
       <c r="AO2" t="n">
-        <v>500.8071428571429</v>
+        <v>-0.01428571428571429</v>
       </c>
       <c r="AP2" t="n">
-        <v>501.3625</v>
+        <v>-0.0625</v>
       </c>
       <c r="AQ2" t="n">
-        <v>500.1555555555556</v>
+        <v>-0.04444444444444445</v>
       </c>
       <c r="AR2" t="n">
-        <v>498.94</v>
+        <v>-0.04</v>
       </c>
       <c r="AS2" t="n">
-        <v>25.05432846835053</v>
+        <v>498</v>
       </c>
       <c r="AT2" t="n">
-        <v>25.03772154170583</v>
+        <v>494.8166666666667</v>
       </c>
       <c r="AU2" t="n">
-        <v>26.74050941455678</v>
+        <v>495</v>
       </c>
       <c r="AV2" t="n">
-        <v>27.31756943800088</v>
+        <v>494</v>
       </c>
       <c r="AW2" t="n">
-        <v>26.96126851615109</v>
+        <v>494.1</v>
       </c>
       <c r="AX2" t="n">
-        <v>27.15403059494152</v>
+        <v>493.7428571428571</v>
       </c>
       <c r="AY2" t="n">
-        <v>27.07085321429674</v>
+        <v>493.725</v>
       </c>
       <c r="AZ2" t="n">
-        <v>27.20290471055174</v>
+        <v>495.4222222222222</v>
       </c>
       <c r="BA2" t="n">
-        <v>27.13478210710379</v>
+        <v>496.365</v>
       </c>
       <c r="BB2" t="n">
-        <v>467</v>
+        <v>45.94888464369946</v>
       </c>
       <c r="BC2" t="n">
-        <v>458</v>
+        <v>43.09582024074054</v>
       </c>
       <c r="BD2" t="n">
-        <v>451</v>
+        <v>39.35924287889695</v>
       </c>
       <c r="BE2" t="n">
-        <v>451</v>
+        <v>37.46625148049909</v>
       </c>
       <c r="BF2" t="n">
-        <v>451</v>
+        <v>36.02438988611281</v>
       </c>
       <c r="BG2" t="n">
-        <v>451</v>
+        <v>34.76705571752238</v>
       </c>
       <c r="BH2" t="n">
-        <v>451</v>
+        <v>33.32265558145089</v>
       </c>
       <c r="BI2" t="n">
-        <v>451</v>
+        <v>32.58628811079141</v>
       </c>
       <c r="BJ2" t="n">
-        <v>451</v>
+        <v>31.92822849767898</v>
       </c>
       <c r="BK2" t="n">
-        <v>637</v>
+        <v>366</v>
       </c>
       <c r="BL2" t="n">
-        <v>637</v>
+        <v>366</v>
       </c>
       <c r="BM2" t="n">
-        <v>637</v>
+        <v>366</v>
       </c>
       <c r="BN2" t="n">
-        <v>637</v>
+        <v>366</v>
       </c>
       <c r="BO2" t="n">
-        <v>637</v>
+        <v>366</v>
       </c>
       <c r="BP2" t="n">
-        <v>637</v>
+        <v>366</v>
       </c>
       <c r="BQ2" t="n">
-        <v>637</v>
+        <v>366</v>
       </c>
       <c r="BR2" t="n">
-        <v>637</v>
+        <v>366</v>
       </c>
       <c r="BS2" t="n">
-        <v>637</v>
+        <v>366</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.375</v>
+        <v>607</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.9230769230769231</v>
+        <v>607</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2380952380952381</v>
+        <v>607</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.5238095238095238</v>
+        <v>607</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.6666666666666666</v>
+        <v>607</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.9090909090909091</v>
+        <v>607</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.9583333333333334</v>
+        <v>607</v>
       </c>
       <c r="CA2" t="n">
+        <v>607</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>607</v>
+      </c>
+      <c r="CC2" t="n">
         <v>0.8</v>
       </c>
-      <c r="CB2" t="n">
-        <v>0.7714285714285715</v>
+      <c r="CD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.896551724137931</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.7941176470588235</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.7837837837837838</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>500.03</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>24.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S01_G4_499_22_ABS1</t>
+          <t>S02_G4_499_21_ABS1</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>499</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>31.13417346182357</v>
       </c>
       <c r="D3" t="n">
-        <v>32.61675315048184</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
         <v>499</v>
@@ -1098,244 +1186,277 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>498.3990589498306</v>
-      </c>
-      <c r="J3" t="n">
-        <v>33.4741870494422</v>
-      </c>
-      <c r="K3" t="n">
-        <v>489.8978175287435</v>
-      </c>
-      <c r="L3" t="n">
-        <v>30.09006224891908</v>
-      </c>
-      <c r="M3" t="n">
-        <v>490.2786772435141</v>
-      </c>
-      <c r="N3" t="n">
-        <v>26.79425679131871</v>
-      </c>
-      <c r="O3" t="n">
-        <v>494.0256459777503</v>
-      </c>
-      <c r="P3" t="n">
-        <v>30.71127835180178</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>496.3544172756862</v>
-      </c>
       <c r="R3" t="n">
-        <v>28.67174846521096</v>
+        <v>502.02</v>
       </c>
       <c r="S3" t="n">
-        <v>499.0639251482448</v>
+        <v>33.26</v>
       </c>
       <c r="T3" t="n">
-        <v>26.21443895760932</v>
+        <v>503.23</v>
       </c>
       <c r="U3" t="n">
-        <v>501.6893402466634</v>
+        <v>27.65</v>
       </c>
       <c r="V3" t="n">
-        <v>24.26599716982896</v>
+        <v>504.26</v>
       </c>
       <c r="W3" t="n">
-        <v>502.0784608292522</v>
+        <v>24.98</v>
       </c>
       <c r="X3" t="n">
-        <v>24.70059450197929</v>
+        <v>503.91</v>
       </c>
       <c r="Y3" t="n">
-        <v>500.0255167009602</v>
+        <v>24.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>24.72692094427502</v>
+        <v>502.09</v>
       </c>
       <c r="AA3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>501.77</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>502.12</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>502.68</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>502.38</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK3" t="n">
         <v>0</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AL3" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AN3" t="n">
         <v>0</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.01666666666666667</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-0.01428571428571429</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.0625</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.04444444444444445</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>498</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>494.8166666666667</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>495</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>494</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>494.1</v>
-      </c>
       <c r="AO3" t="n">
-        <v>493.7428571428571</v>
+        <v>-0.02857142857142857</v>
       </c>
       <c r="AP3" t="n">
-        <v>493.725</v>
+        <v>-0.025</v>
       </c>
       <c r="AQ3" t="n">
-        <v>495.4222222222222</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>496.365</v>
+        <v>-0.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>45.94888464369946</v>
+        <v>495.95</v>
       </c>
       <c r="AT3" t="n">
-        <v>43.09582024074054</v>
+        <v>499.45</v>
       </c>
       <c r="AU3" t="n">
-        <v>39.35924287889695</v>
+        <v>500.0125</v>
       </c>
       <c r="AV3" t="n">
-        <v>37.46625148049909</v>
+        <v>500.59</v>
       </c>
       <c r="AW3" t="n">
-        <v>36.02438988611281</v>
+        <v>501.1666666666667</v>
       </c>
       <c r="AX3" t="n">
-        <v>34.76705571752238</v>
+        <v>500.3785714285714</v>
       </c>
       <c r="AY3" t="n">
-        <v>33.32265558145089</v>
+        <v>500.9125</v>
       </c>
       <c r="AZ3" t="n">
-        <v>32.58628811079141</v>
+        <v>501.4444444444445</v>
       </c>
       <c r="BA3" t="n">
-        <v>31.92822849767898</v>
+        <v>501.355</v>
       </c>
       <c r="BB3" t="n">
-        <v>366</v>
+        <v>46.30116089257374</v>
       </c>
       <c r="BC3" t="n">
-        <v>366</v>
+        <v>41.89885638853007</v>
       </c>
       <c r="BD3" t="n">
-        <v>366</v>
+        <v>38.44622665164945</v>
       </c>
       <c r="BE3" t="n">
-        <v>366</v>
+        <v>35.46522099183932</v>
       </c>
       <c r="BF3" t="n">
-        <v>366</v>
+        <v>33.86574801903671</v>
       </c>
       <c r="BG3" t="n">
-        <v>366</v>
+        <v>32.73933149180985</v>
       </c>
       <c r="BH3" t="n">
-        <v>366</v>
+        <v>31.81418463123014</v>
       </c>
       <c r="BI3" t="n">
-        <v>366</v>
+        <v>31.03711438158842</v>
       </c>
       <c r="BJ3" t="n">
-        <v>366</v>
+        <v>30.44780739232301</v>
       </c>
       <c r="BK3" t="n">
-        <v>607</v>
+        <v>352</v>
       </c>
       <c r="BL3" t="n">
-        <v>607</v>
+        <v>352</v>
       </c>
       <c r="BM3" t="n">
-        <v>607</v>
+        <v>352</v>
       </c>
       <c r="BN3" t="n">
-        <v>607</v>
+        <v>352</v>
       </c>
       <c r="BO3" t="n">
-        <v>607</v>
+        <v>352</v>
       </c>
       <c r="BP3" t="n">
-        <v>607</v>
+        <v>352</v>
       </c>
       <c r="BQ3" t="n">
-        <v>607</v>
+        <v>352</v>
       </c>
       <c r="BR3" t="n">
-        <v>607</v>
+        <v>352</v>
       </c>
       <c r="BS3" t="n">
-        <v>607</v>
+        <v>352</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.8</v>
+        <v>606</v>
       </c>
       <c r="BU3" t="n">
-        <v>1</v>
+        <v>606</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.8571428571428571</v>
+        <v>606</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.8421052631578947</v>
+        <v>606</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.875</v>
+        <v>606</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.896551724137931</v>
+        <v>606</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.84375</v>
+        <v>606</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.7941176470588235</v>
+        <v>606</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.7837837837837838</v>
+        <v>606</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.7027027027027027</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>502.38</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>23.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S02_G4_499_21_ABS1</t>
+          <t>S03_G4_499_20_ABS1</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>499</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D4" t="n">
-        <v>31.13417346182357</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
         <v>499</v>
@@ -1344,228 +1465,261 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>502.0174288538207</v>
-      </c>
-      <c r="J4" t="n">
-        <v>33.2569531861958</v>
-      </c>
-      <c r="K4" t="n">
-        <v>503.2250781911448</v>
-      </c>
-      <c r="L4" t="n">
-        <v>27.64597980001324</v>
-      </c>
-      <c r="M4" t="n">
-        <v>504.2644101075042</v>
-      </c>
-      <c r="N4" t="n">
-        <v>24.98415052674509</v>
-      </c>
-      <c r="O4" t="n">
-        <v>503.9130449244508</v>
-      </c>
-      <c r="P4" t="n">
-        <v>24.53207713857703</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>502.0877806430897</v>
-      </c>
       <c r="R4" t="n">
-        <v>24.60167900744367</v>
+        <v>507.14</v>
       </c>
       <c r="S4" t="n">
-        <v>501.7675291004965</v>
+        <v>18.92</v>
       </c>
       <c r="T4" t="n">
-        <v>24.63801346583397</v>
+        <v>505.35</v>
       </c>
       <c r="U4" t="n">
-        <v>502.1211613794554</v>
+        <v>14.14</v>
       </c>
       <c r="V4" t="n">
-        <v>23.82355086274758</v>
+        <v>497.83</v>
       </c>
       <c r="W4" t="n">
-        <v>502.6814052037326</v>
+        <v>21.63</v>
       </c>
       <c r="X4" t="n">
-        <v>23.31994839040777</v>
+        <v>498.61</v>
       </c>
       <c r="Y4" t="n">
-        <v>502.3801597845476</v>
+        <v>23.72</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.71253021890209</v>
+        <v>498.57</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05</v>
+        <v>22.21</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>499.07</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.025</v>
+        <v>23.96</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.02</v>
+        <v>500.68</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>24.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.02857142857142857</v>
+        <v>499.41</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.025</v>
+        <v>24.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>498.11</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.01</v>
+        <v>24.93</v>
       </c>
       <c r="AJ4" t="n">
-        <v>495.95</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="AK4" t="n">
-        <v>499.45</v>
+        <v>0.559322033898305</v>
       </c>
       <c r="AL4" t="n">
-        <v>500.0125</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="AM4" t="n">
-        <v>500.59</v>
+        <v>0.08163265306122448</v>
       </c>
       <c r="AN4" t="n">
-        <v>501.1666666666667</v>
+        <v>0.1016949152542373</v>
       </c>
       <c r="AO4" t="n">
-        <v>500.3785714285714</v>
+        <v>0.1159420289855072</v>
       </c>
       <c r="AP4" t="n">
-        <v>500.9125</v>
+        <v>0.1392405063291139</v>
       </c>
       <c r="AQ4" t="n">
-        <v>501.4444444444445</v>
+        <v>0.0898876404494382</v>
       </c>
       <c r="AR4" t="n">
-        <v>501.355</v>
+        <v>0.0505050505050505</v>
       </c>
       <c r="AS4" t="n">
-        <v>46.30116089257374</v>
+        <v>508.325</v>
       </c>
       <c r="AT4" t="n">
-        <v>41.89885638853007</v>
+        <v>511.75</v>
       </c>
       <c r="AU4" t="n">
-        <v>38.44622665164945</v>
+        <v>504.2875</v>
       </c>
       <c r="AV4" t="n">
-        <v>35.46522099183932</v>
+        <v>500.48</v>
       </c>
       <c r="AW4" t="n">
-        <v>33.86574801903671</v>
+        <v>500.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>32.73933149180985</v>
+        <v>500.8071428571429</v>
       </c>
       <c r="AY4" t="n">
-        <v>31.81418463123014</v>
+        <v>501.3625</v>
       </c>
       <c r="AZ4" t="n">
-        <v>31.03711438158842</v>
+        <v>500.1555555555556</v>
       </c>
       <c r="BA4" t="n">
-        <v>30.44780739232301</v>
+        <v>498.94</v>
       </c>
       <c r="BB4" t="n">
-        <v>352</v>
+        <v>25.05432846835053</v>
       </c>
       <c r="BC4" t="n">
-        <v>352</v>
+        <v>25.03772154170583</v>
       </c>
       <c r="BD4" t="n">
-        <v>352</v>
+        <v>26.74050941455678</v>
       </c>
       <c r="BE4" t="n">
-        <v>352</v>
+        <v>27.31756943800088</v>
       </c>
       <c r="BF4" t="n">
-        <v>352</v>
+        <v>26.96126851615109</v>
       </c>
       <c r="BG4" t="n">
-        <v>352</v>
+        <v>27.15403059494152</v>
       </c>
       <c r="BH4" t="n">
-        <v>352</v>
+        <v>27.07085321429674</v>
       </c>
       <c r="BI4" t="n">
-        <v>352</v>
+        <v>27.20290471055174</v>
       </c>
       <c r="BJ4" t="n">
-        <v>352</v>
+        <v>27.13478210710379</v>
       </c>
       <c r="BK4" t="n">
-        <v>606</v>
+        <v>467</v>
       </c>
       <c r="BL4" t="n">
-        <v>606</v>
+        <v>458</v>
       </c>
       <c r="BM4" t="n">
-        <v>606</v>
+        <v>451</v>
       </c>
       <c r="BN4" t="n">
-        <v>606</v>
+        <v>451</v>
       </c>
       <c r="BO4" t="n">
-        <v>606</v>
+        <v>451</v>
       </c>
       <c r="BP4" t="n">
-        <v>606</v>
+        <v>451</v>
       </c>
       <c r="BQ4" t="n">
-        <v>606</v>
+        <v>451</v>
       </c>
       <c r="BR4" t="n">
-        <v>606</v>
+        <v>451</v>
       </c>
       <c r="BS4" t="n">
-        <v>606</v>
+        <v>451</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.7142857142857143</v>
+        <v>637</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.7</v>
+        <v>637</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.7333333333333333</v>
+        <v>637</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.6818181818181818</v>
+        <v>637</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.6785714285714286</v>
+        <v>637</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.7575757575757576</v>
+        <v>637</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.7027027027027027</v>
+        <v>637</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.775</v>
+        <v>637</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.7391304347826086</v>
+        <v>637</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>498.11</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>24.93</v>
       </c>
     </row>
     <row r="5">
@@ -1578,10 +1732,10 @@
         <v>499</v>
       </c>
       <c r="C5" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D5" t="n">
         <v>21</v>
-      </c>
-      <c r="D5" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E5" t="n">
         <v>499</v>
@@ -1590,244 +1744,277 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>483.8566061946244</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15.17381342497219</v>
-      </c>
-      <c r="K5" t="n">
-        <v>483.6067651687746</v>
-      </c>
-      <c r="L5" t="n">
-        <v>14.90436003775279</v>
-      </c>
-      <c r="M5" t="n">
-        <v>491.4709799321</v>
-      </c>
-      <c r="N5" t="n">
-        <v>21.98905820132145</v>
-      </c>
-      <c r="O5" t="n">
-        <v>492.6416933470582</v>
-      </c>
-      <c r="P5" t="n">
-        <v>22.67422171518057</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>493.6899631688997</v>
-      </c>
       <c r="R5" t="n">
-        <v>20.76144683658876</v>
+        <v>483.86</v>
       </c>
       <c r="S5" t="n">
-        <v>493.2209777674881</v>
+        <v>15.17</v>
       </c>
       <c r="T5" t="n">
-        <v>22.02800596337136</v>
+        <v>483.61</v>
       </c>
       <c r="U5" t="n">
-        <v>493.6349970125951</v>
+        <v>14.9</v>
       </c>
       <c r="V5" t="n">
-        <v>21.62905719553374</v>
+        <v>491.47</v>
       </c>
       <c r="W5" t="n">
-        <v>492.6903690335502</v>
+        <v>21.99</v>
       </c>
       <c r="X5" t="n">
-        <v>22.36138526644334</v>
+        <v>492.64</v>
       </c>
       <c r="Y5" t="n">
-        <v>493.5732094493634</v>
+        <v>22.67</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.50260976399481</v>
+        <v>493.69</v>
       </c>
       <c r="AA5" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>493.22</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>493.63</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>492.69</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>493.57</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>-0.65</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AK5" t="n">
         <v>-0.5666666666666667</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AL5" t="n">
         <v>-0.375</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AM5" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AN5" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AO5" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AP5" t="n">
         <v>-0.075</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AQ5" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AR5" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AS5" t="n">
         <v>478.875</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AT5" t="n">
         <v>479.6666666666667</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AU5" t="n">
         <v>484.5125</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AV5" t="n">
         <v>491.48</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AW5" t="n">
         <v>492.6583333333334</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AX5" t="n">
         <v>492.4357142857143</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AY5" t="n">
         <v>492.86875</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AZ5" t="n">
         <v>492.2</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="BA5" t="n">
         <v>492.27</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="BB5" t="n">
         <v>28.33565554209043</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BC5" t="n">
         <v>25.45300680775368</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="BD5" t="n">
         <v>25.22151549272962</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="BE5" t="n">
         <v>27.89784221046495</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BF5" t="n">
         <v>27.11656806988836</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BG5" t="n">
         <v>26.34149651738698</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BH5" t="n">
         <v>25.63033404849613</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BI5" t="n">
         <v>25.69184911817581</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BJ5" t="n">
         <v>25.27127024903972</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BK5" t="n">
         <v>356</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BL5" t="n">
         <v>356</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BM5" t="n">
         <v>356</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BN5" t="n">
         <v>356</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BO5" t="n">
         <v>356</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BP5" t="n">
         <v>356</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BQ5" t="n">
         <v>356</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BR5" t="n">
         <v>356</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BS5" t="n">
         <v>356</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BT5" t="n">
         <v>522</v>
       </c>
-      <c r="BL5" t="n">
+      <c r="BU5" t="n">
         <v>522</v>
       </c>
-      <c r="BM5" t="n">
+      <c r="BV5" t="n">
         <v>522</v>
       </c>
-      <c r="BN5" t="n">
+      <c r="BW5" t="n">
         <v>535</v>
       </c>
-      <c r="BO5" t="n">
+      <c r="BX5" t="n">
         <v>535</v>
       </c>
-      <c r="BP5" t="n">
+      <c r="BY5" t="n">
         <v>535</v>
       </c>
-      <c r="BQ5" t="n">
+      <c r="BZ5" t="n">
         <v>535</v>
       </c>
-      <c r="BR5" t="n">
+      <c r="CA5" t="n">
         <v>535</v>
       </c>
-      <c r="BS5" t="n">
+      <c r="CB5" t="n">
         <v>535</v>
       </c>
-      <c r="BT5" t="n">
+      <c r="CC5" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="CD5" t="n">
         <v>0.4</v>
       </c>
-      <c r="BV5" t="n">
+      <c r="CE5" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="CF5" t="n">
         <v>0.875</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="CG5" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="CH5" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="CI5" t="n">
         <v>0.967741935483871</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CJ5" t="n">
         <v>0.8857142857142857</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="CK5" t="n">
         <v>0.9210526315789473</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>493.57</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>20.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S06_G4_499_22_ABS1</t>
+          <t>S05_G4_499_20_ABS1</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>499</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D6" t="n">
-        <v>32.61675315048184</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
         <v>499</v>
@@ -1836,244 +2023,277 @@
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>505.064143423186</v>
-      </c>
-      <c r="J6" t="n">
-        <v>15.16633740817083</v>
-      </c>
-      <c r="K6" t="n">
-        <v>504.5696622239784</v>
-      </c>
-      <c r="L6" t="n">
-        <v>27.59957550398896</v>
-      </c>
-      <c r="M6" t="n">
-        <v>506.2852791949275</v>
-      </c>
-      <c r="N6" t="n">
-        <v>30.82921896257036</v>
-      </c>
-      <c r="O6" t="n">
-        <v>506.1801033776097</v>
-      </c>
-      <c r="P6" t="n">
-        <v>26.72534540282391</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>507.0098963737652</v>
-      </c>
       <c r="R6" t="n">
-        <v>25.59236744034633</v>
+        <v>499.42</v>
       </c>
       <c r="S6" t="n">
-        <v>507.8271638952531</v>
+        <v>39.69</v>
       </c>
       <c r="T6" t="n">
-        <v>26.65462142962295</v>
+        <v>500.32</v>
       </c>
       <c r="U6" t="n">
-        <v>507.6115276787788</v>
+        <v>28.75</v>
       </c>
       <c r="V6" t="n">
-        <v>25.17654913395177</v>
+        <v>499.62</v>
       </c>
       <c r="W6" t="n">
-        <v>507.3342724015559</v>
+        <v>33.21</v>
       </c>
       <c r="X6" t="n">
-        <v>24.63302709016414</v>
+        <v>500.53</v>
       </c>
       <c r="Y6" t="n">
-        <v>505.3424180017824</v>
+        <v>27.69</v>
       </c>
       <c r="Z6" t="n">
-        <v>25.5214808497486</v>
+        <v>497.39</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4358974358974359</v>
+        <v>29.82</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1864406779661017</v>
+        <v>495.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2405063291139241</v>
+        <v>27.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.1717171717171717</v>
+        <v>493.65</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1428571428571428</v>
+        <v>25.65</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1223021582733813</v>
+        <v>493.97</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.09433962264150944</v>
+        <v>26.83</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.07865168539325842</v>
+        <v>493.05</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.06060606060606061</v>
+        <v>26.65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>501.475</v>
+        <v>0.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>499.1333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>505.05</v>
+        <v>0.05</v>
       </c>
       <c r="AM6" t="n">
-        <v>504.08</v>
+        <v>-0.02</v>
       </c>
       <c r="AN6" t="n">
-        <v>505.2083333333333</v>
+        <v>-0.01666666666666667</v>
       </c>
       <c r="AO6" t="n">
-        <v>505.3642857142857</v>
+        <v>-0.02857142857142857</v>
       </c>
       <c r="AP6" t="n">
-        <v>505.54375</v>
+        <v>-0.025</v>
       </c>
       <c r="AQ6" t="n">
-        <v>505.5555555555555</v>
+        <v>-0.01111111111111111</v>
       </c>
       <c r="AR6" t="n">
-        <v>504.99</v>
+        <v>-0.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>27.10810533770297</v>
+        <v>503.875</v>
       </c>
       <c r="AT6" t="n">
-        <v>30.68847050965919</v>
+        <v>497</v>
       </c>
       <c r="AU6" t="n">
-        <v>34.95636565777398</v>
+        <v>497.225</v>
       </c>
       <c r="AV6" t="n">
-        <v>34.28080512473416</v>
+        <v>496.62</v>
       </c>
       <c r="AW6" t="n">
-        <v>33.41703553412374</v>
+        <v>497.3666666666667</v>
       </c>
       <c r="AX6" t="n">
-        <v>32.30528720863897</v>
+        <v>497.1714285714286</v>
       </c>
       <c r="AY6" t="n">
-        <v>31.59526208053195</v>
+        <v>497.05625</v>
       </c>
       <c r="AZ6" t="n">
-        <v>30.96884137003626</v>
+        <v>496.9277777777778</v>
       </c>
       <c r="BA6" t="n">
-        <v>30.54226415968535</v>
+        <v>496.385</v>
       </c>
       <c r="BB6" t="n">
-        <v>367</v>
+        <v>40.48591576091616</v>
       </c>
       <c r="BC6" t="n">
-        <v>367</v>
+        <v>40.84850058447678</v>
       </c>
       <c r="BD6" t="n">
-        <v>367</v>
+        <v>39.93963413703235</v>
       </c>
       <c r="BE6" t="n">
-        <v>367</v>
+        <v>38.17742264742343</v>
       </c>
       <c r="BF6" t="n">
-        <v>367</v>
+        <v>36.31641808083807</v>
       </c>
       <c r="BG6" t="n">
-        <v>367</v>
+        <v>35.33653367613889</v>
       </c>
       <c r="BH6" t="n">
-        <v>367</v>
+        <v>34.28269367971981</v>
       </c>
       <c r="BI6" t="n">
-        <v>367</v>
+        <v>33.42620903747962</v>
       </c>
       <c r="BJ6" t="n">
-        <v>367</v>
+        <v>32.71325075561889</v>
       </c>
       <c r="BK6" t="n">
-        <v>541</v>
+        <v>435</v>
       </c>
       <c r="BL6" t="n">
-        <v>555</v>
+        <v>435</v>
       </c>
       <c r="BM6" t="n">
-        <v>565</v>
+        <v>435</v>
       </c>
       <c r="BN6" t="n">
-        <v>565</v>
+        <v>435</v>
       </c>
       <c r="BO6" t="n">
-        <v>565</v>
+        <v>435</v>
       </c>
       <c r="BP6" t="n">
-        <v>565</v>
+        <v>435</v>
       </c>
       <c r="BQ6" t="n">
-        <v>565</v>
+        <v>435</v>
       </c>
       <c r="BR6" t="n">
-        <v>565</v>
+        <v>435</v>
       </c>
       <c r="BS6" t="n">
-        <v>565</v>
+        <v>435</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.6153846153846154</v>
+        <v>653</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.4615384615384616</v>
+        <v>653</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.9166666666666666</v>
+        <v>653</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.7647058823529411</v>
+        <v>653</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.95</v>
+        <v>653</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.9130434782608695</v>
+        <v>653</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.9230769230769231</v>
+        <v>653</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.9</v>
+        <v>653</v>
       </c>
       <c r="CB6" t="n">
+        <v>653</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="CG6" t="n">
         <v>0.7777777777777778</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>493.05</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>26.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S05_G4_499_20_ABS1</t>
+          <t>S06_G4_499_22_ABS1</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>499</v>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>32.61675315048184</v>
       </c>
       <c r="D7" t="n">
-        <v>29.65159377316531</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
         <v>499</v>
@@ -2082,228 +2302,261 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>499.421912437135</v>
-      </c>
-      <c r="J7" t="n">
-        <v>39.69177093734443</v>
-      </c>
-      <c r="K7" t="n">
-        <v>500.3223878761318</v>
-      </c>
-      <c r="L7" t="n">
-        <v>28.75382254542556</v>
-      </c>
-      <c r="M7" t="n">
-        <v>499.6237224028851</v>
-      </c>
-      <c r="N7" t="n">
-        <v>33.20723251639433</v>
-      </c>
-      <c r="O7" t="n">
-        <v>500.5311737787365</v>
-      </c>
-      <c r="P7" t="n">
-        <v>27.69242658747429</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>497.3922876417361</v>
-      </c>
       <c r="R7" t="n">
-        <v>29.81898809564637</v>
+        <v>505.06</v>
       </c>
       <c r="S7" t="n">
-        <v>495.1253229824346</v>
+        <v>15.17</v>
       </c>
       <c r="T7" t="n">
-        <v>27.59502723298528</v>
+        <v>504.57</v>
       </c>
       <c r="U7" t="n">
-        <v>493.654117205301</v>
+        <v>27.6</v>
       </c>
       <c r="V7" t="n">
-        <v>25.65117645155834</v>
+        <v>506.29</v>
       </c>
       <c r="W7" t="n">
-        <v>493.9725963719545</v>
+        <v>30.83</v>
       </c>
       <c r="X7" t="n">
-        <v>26.83227616559781</v>
+        <v>506.18</v>
       </c>
       <c r="Y7" t="n">
-        <v>493.054123419379</v>
+        <v>26.73</v>
       </c>
       <c r="Z7" t="n">
-        <v>26.64756646956452</v>
+        <v>507.01</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4</v>
+        <v>25.59</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1</v>
+        <v>507.83</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05</v>
+        <v>26.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.02</v>
+        <v>507.61</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.01666666666666667</v>
+        <v>25.18</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.02857142857142857</v>
+        <v>507.33</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.025</v>
+        <v>24.63</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.01111111111111111</v>
+        <v>505.34</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.01</v>
+        <v>25.52</v>
       </c>
       <c r="AJ7" t="n">
-        <v>503.875</v>
+        <v>0.4358974358974359</v>
       </c>
       <c r="AK7" t="n">
-        <v>497</v>
+        <v>0.1864406779661017</v>
       </c>
       <c r="AL7" t="n">
-        <v>497.225</v>
+        <v>0.2405063291139241</v>
       </c>
       <c r="AM7" t="n">
-        <v>496.62</v>
+        <v>0.1717171717171717</v>
       </c>
       <c r="AN7" t="n">
-        <v>497.3666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO7" t="n">
-        <v>497.1714285714286</v>
+        <v>0.1223021582733813</v>
       </c>
       <c r="AP7" t="n">
-        <v>497.05625</v>
+        <v>0.09433962264150944</v>
       </c>
       <c r="AQ7" t="n">
-        <v>496.9277777777778</v>
+        <v>0.07865168539325842</v>
       </c>
       <c r="AR7" t="n">
-        <v>496.385</v>
+        <v>0.06060606060606061</v>
       </c>
       <c r="AS7" t="n">
-        <v>40.48591576091616</v>
+        <v>501.475</v>
       </c>
       <c r="AT7" t="n">
-        <v>40.84850058447678</v>
+        <v>499.1333333333333</v>
       </c>
       <c r="AU7" t="n">
-        <v>39.93963413703235</v>
+        <v>505.05</v>
       </c>
       <c r="AV7" t="n">
-        <v>38.17742264742343</v>
+        <v>504.08</v>
       </c>
       <c r="AW7" t="n">
-        <v>36.31641808083807</v>
+        <v>505.2083333333333</v>
       </c>
       <c r="AX7" t="n">
-        <v>35.33653367613889</v>
+        <v>505.3642857142857</v>
       </c>
       <c r="AY7" t="n">
-        <v>34.28269367971981</v>
+        <v>505.54375</v>
       </c>
       <c r="AZ7" t="n">
-        <v>33.42620903747962</v>
+        <v>505.5555555555555</v>
       </c>
       <c r="BA7" t="n">
-        <v>32.71325075561889</v>
+        <v>504.99</v>
       </c>
       <c r="BB7" t="n">
-        <v>435</v>
+        <v>27.10810533770297</v>
       </c>
       <c r="BC7" t="n">
-        <v>435</v>
+        <v>30.68847050965919</v>
       </c>
       <c r="BD7" t="n">
-        <v>435</v>
+        <v>34.95636565777398</v>
       </c>
       <c r="BE7" t="n">
-        <v>435</v>
+        <v>34.28080512473416</v>
       </c>
       <c r="BF7" t="n">
-        <v>435</v>
+        <v>33.41703553412374</v>
       </c>
       <c r="BG7" t="n">
-        <v>435</v>
+        <v>32.30528720863897</v>
       </c>
       <c r="BH7" t="n">
-        <v>435</v>
+        <v>31.59526208053195</v>
       </c>
       <c r="BI7" t="n">
-        <v>435</v>
+        <v>30.96884137003626</v>
       </c>
       <c r="BJ7" t="n">
-        <v>435</v>
+        <v>30.54226415968535</v>
       </c>
       <c r="BK7" t="n">
-        <v>653</v>
+        <v>367</v>
       </c>
       <c r="BL7" t="n">
-        <v>653</v>
+        <v>367</v>
       </c>
       <c r="BM7" t="n">
-        <v>653</v>
+        <v>367</v>
       </c>
       <c r="BN7" t="n">
-        <v>653</v>
+        <v>367</v>
       </c>
       <c r="BO7" t="n">
-        <v>653</v>
+        <v>367</v>
       </c>
       <c r="BP7" t="n">
-        <v>653</v>
+        <v>367</v>
       </c>
       <c r="BQ7" t="n">
-        <v>653</v>
+        <v>367</v>
       </c>
       <c r="BR7" t="n">
-        <v>653</v>
+        <v>367</v>
       </c>
       <c r="BS7" t="n">
-        <v>653</v>
+        <v>367</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.09090909090909091</v>
+        <v>541</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.6363636363636364</v>
+        <v>555</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.8461538461538461</v>
+        <v>565</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.6470588235294118</v>
+        <v>565</v>
       </c>
       <c r="BX7" t="n">
+        <v>565</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>565</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>565</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>565</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>565</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.9130434782608695</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CK7" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BY7" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0.9354838709677419</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>0.9142857142857143</v>
+      <c r="CL7" t="n">
+        <v>505.34</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>25.52</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>502</v>
       </c>
       <c r="C8" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D8" t="n">
         <v>21</v>
-      </c>
-      <c r="D8" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E8" t="n">
         <v>502</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>506.3253902325092</v>
-      </c>
-      <c r="J8" t="n">
-        <v>17.45653666136893</v>
-      </c>
-      <c r="K8" t="n">
-        <v>510.3518694414288</v>
-      </c>
-      <c r="L8" t="n">
-        <v>18.53855430075949</v>
-      </c>
-      <c r="M8" t="n">
-        <v>505.0108859560556</v>
-      </c>
-      <c r="N8" t="n">
-        <v>22.0980565876151</v>
-      </c>
-      <c r="O8" t="n">
-        <v>504.1574233524245</v>
-      </c>
-      <c r="P8" t="n">
-        <v>20.32331830328254</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>502.1628234767601</v>
-      </c>
       <c r="R8" t="n">
-        <v>24.07673326859311</v>
+        <v>506.33</v>
       </c>
       <c r="S8" t="n">
-        <v>501.8981788664586</v>
+        <v>17.46</v>
       </c>
       <c r="T8" t="n">
-        <v>22.07475017011391</v>
+        <v>510.35</v>
       </c>
       <c r="U8" t="n">
-        <v>502.6183264921727</v>
+        <v>18.54</v>
       </c>
       <c r="V8" t="n">
-        <v>21.77412962522317</v>
+        <v>505.01</v>
       </c>
       <c r="W8" t="n">
-        <v>503.7351573823242</v>
+        <v>22.1</v>
       </c>
       <c r="X8" t="n">
-        <v>21.95393404289063</v>
+        <v>504.16</v>
       </c>
       <c r="Y8" t="n">
-        <v>503.3159082821526</v>
+        <v>20.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.70781756407253</v>
+        <v>502.16</v>
       </c>
       <c r="AA8" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>501.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>22.07</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>502.62</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>503.74</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>503.32</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>0.1</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AK8" t="n">
         <v>0.2666666666666667</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AL8" t="n">
         <v>0.1</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AM8" t="n">
         <v>0.1</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AN8" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AO8" t="n">
         <v>0.05714285714285714</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AP8" t="n">
         <v>0.075</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AQ8" t="n">
         <v>0.04444444444444445</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AR8" t="n">
         <v>0.05</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AS8" t="n">
         <v>505.35</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>508.75</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>505.55</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>505.53</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>503.725</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>503.7571428571429</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>504.08125</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>503.5388888888889</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>503.58</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>37.62017410911331</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>32.71473928776854</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>31.4876563116406</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>30.25209248961136</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>29.51495736628012</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>28.75459501877705</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>27.98771424102904</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>27.50785017022694</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>26.91437534107006</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>369</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>369</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>369</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>369</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>369</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>369</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>369</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>369</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>369</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BT8" t="n">
         <v>604</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BU8" t="n">
         <v>604</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BV8" t="n">
         <v>604</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BW8" t="n">
         <v>604</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BX8" t="n">
         <v>604</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BY8" t="n">
         <v>604</v>
       </c>
-      <c r="BQ8" t="n">
+      <c r="BZ8" t="n">
         <v>604</v>
       </c>
-      <c r="BR8" t="n">
+      <c r="CA8" t="n">
         <v>604</v>
       </c>
-      <c r="BS8" t="n">
+      <c r="CB8" t="n">
         <v>604</v>
       </c>
-      <c r="BT8" t="n">
+      <c r="CC8" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>1</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.04761904761904762</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.84</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.9310344827586207</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.8055555555555556</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.825</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>503.32</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>20.71</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>502</v>
       </c>
       <c r="C9" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D9" t="n">
         <v>18</v>
-      </c>
-      <c r="D9" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E9" t="n">
         <v>502</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>72</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>506.3206032594379</v>
-      </c>
-      <c r="J9" t="n">
-        <v>17.36381177611865</v>
-      </c>
-      <c r="K9" t="n">
-        <v>507.0148334861519</v>
-      </c>
-      <c r="L9" t="n">
-        <v>16.02006401888454</v>
-      </c>
-      <c r="M9" t="n">
-        <v>506.937738117299</v>
-      </c>
-      <c r="N9" t="n">
-        <v>18.84290429518136</v>
-      </c>
-      <c r="O9" t="n">
-        <v>504.6388669087721</v>
-      </c>
-      <c r="P9" t="n">
-        <v>19.85676016948341</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>505.3637177758341</v>
-      </c>
       <c r="R9" t="n">
-        <v>19.45617143417488</v>
+        <v>506.32</v>
       </c>
       <c r="S9" t="n">
-        <v>504.3610998324624</v>
+        <v>17.36</v>
       </c>
       <c r="T9" t="n">
-        <v>20.18156261748051</v>
+        <v>507.01</v>
       </c>
       <c r="U9" t="n">
-        <v>503.1483651030816</v>
+        <v>16.02</v>
       </c>
       <c r="V9" t="n">
-        <v>20.87012460506861</v>
+        <v>506.94</v>
       </c>
       <c r="W9" t="n">
-        <v>501.8384807951164</v>
+        <v>18.84</v>
       </c>
       <c r="X9" t="n">
-        <v>21.84938671712979</v>
+        <v>504.64</v>
       </c>
       <c r="Y9" t="n">
-        <v>501.9791798096227</v>
+        <v>19.86</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.29523127676778</v>
+        <v>505.36</v>
       </c>
       <c r="AA9" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>504.36</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>503.15</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>20.87</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>501.84</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>501.98</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>0.15</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AK9" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AL9" t="n">
         <v>0.175</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AM9" t="n">
         <v>0.1313131313131313</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AN9" t="n">
         <v>0.1092436974789916</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AO9" t="n">
         <v>0.09352517985611511</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AP9" t="n">
         <v>0.08176100628930817</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AQ9" t="n">
         <v>0.05027932960893855</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AR9" t="n">
         <v>0.04522613065326633</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AS9" t="n">
         <v>500.35</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>504.2833333333334</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>505.7125</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>504.73</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>504.675</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>504.4714285714286</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>504.43125</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>503.6611111111111</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>503.625</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>40.32589118668055</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>36.30247542829858</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>33.48103707697837</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>31.49471542973519</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>30.11510210841066</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>29.09355423387084</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>28.22401944155899</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>27.60397795183571</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>27.0607534078414</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>355</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>355</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>355</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>355</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>355</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>355</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>355</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>355</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>355</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BT9" t="n">
         <v>640</v>
       </c>
-      <c r="BL9" t="n">
+      <c r="BU9" t="n">
         <v>640</v>
       </c>
-      <c r="BM9" t="n">
+      <c r="BV9" t="n">
         <v>640</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BW9" t="n">
         <v>640</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BX9" t="n">
         <v>640</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BY9" t="n">
         <v>640</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BZ9" t="n">
         <v>640</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="CA9" t="n">
         <v>640</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="CB9" t="n">
         <v>640</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="CC9" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.9545454545454546</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.9629629629629629</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.9696969696969697</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>1</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.9512195121951219</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.9777777777777777</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>501.98</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>22.3</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>502</v>
       </c>
       <c r="C10" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D10" t="n">
         <v>18</v>
-      </c>
-      <c r="D10" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E10" t="n">
         <v>502</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>498.6504364264966</v>
-      </c>
-      <c r="J10" t="n">
-        <v>11.2548787329719</v>
-      </c>
-      <c r="K10" t="n">
-        <v>500.5205809572418</v>
-      </c>
-      <c r="L10" t="n">
-        <v>15.60565361980452</v>
-      </c>
-      <c r="M10" t="n">
-        <v>500.0110571126276</v>
-      </c>
-      <c r="N10" t="n">
-        <v>18.10759405465294</v>
-      </c>
-      <c r="O10" t="n">
-        <v>498.3973431825711</v>
-      </c>
-      <c r="P10" t="n">
-        <v>17.63854964231127</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>498.1377865269018</v>
-      </c>
       <c r="R10" t="n">
-        <v>18.56788313098843</v>
+        <v>498.65</v>
       </c>
       <c r="S10" t="n">
-        <v>499.0058882592605</v>
+        <v>11.25</v>
       </c>
       <c r="T10" t="n">
-        <v>19.28796667764517</v>
+        <v>500.52</v>
       </c>
       <c r="U10" t="n">
-        <v>500.4880422705984</v>
+        <v>15.61</v>
       </c>
       <c r="V10" t="n">
-        <v>19.22748658435355</v>
+        <v>500.01</v>
       </c>
       <c r="W10" t="n">
-        <v>500.3644248842892</v>
+        <v>18.11</v>
       </c>
       <c r="X10" t="n">
-        <v>18.64909865375006</v>
+        <v>498.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>500.2089207892918</v>
+        <v>17.64</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.53047188748501</v>
+        <v>498.14</v>
       </c>
       <c r="AA10" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>499.01</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>500.49</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>500.36</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>500.21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>-0.1794871794871795</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AK10" t="n">
         <v>0.05084745762711865</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AL10" t="n">
         <v>0.01265822784810127</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AM10" t="n">
         <v>-0.0505050505050505</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AN10" t="n">
         <v>-0.05882352941176471</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AO10" t="n">
         <v>-0.02158273381294964</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AP10" t="n">
         <v>0.006289308176100629</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AQ10" t="n">
         <v>0.00558659217877095</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AR10" t="n">
         <v>0.005025125628140704</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AS10" t="n">
         <v>490.975</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>497.3</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>497.5125</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>496.63</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>496.725</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>497.6357142857143</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>498.15</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>498.2666666666667</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>498.34</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>25.35003698222155</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>25.42721638979252</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>24.82538708157438</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>23.80195580199241</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>23.65972756253405</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>23.34346366583947</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>23.15307754921579</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>22.99893717351111</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>22.64540571506724</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>361</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>361</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>361</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>361</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>361</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>361</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>361</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>361</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>361</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BT10" t="n">
         <v>519</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BU10" t="n">
         <v>534</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BV10" t="n">
         <v>535</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BW10" t="n">
         <v>535</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BX10" t="n">
         <v>535</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BY10" t="n">
         <v>535</v>
       </c>
-      <c r="BQ10" t="n">
+      <c r="BZ10" t="n">
         <v>535</v>
       </c>
-      <c r="BR10" t="n">
+      <c r="CA10" t="n">
         <v>535</v>
       </c>
-      <c r="BS10" t="n">
+      <c r="CB10" t="n">
         <v>535</v>
       </c>
-      <c r="BT10" t="n">
+      <c r="CC10" t="n">
         <v>0</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.875</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.8</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.6956521739130435</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.75</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.9259259259259259</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.9393939393939394</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>500.21</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>17.53</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>500</v>
       </c>
       <c r="C11" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D11" t="n">
         <v>19</v>
-      </c>
-      <c r="D11" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E11" t="n">
         <v>500</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>499.3272218550092</v>
-      </c>
-      <c r="J11" t="n">
-        <v>19.03278120987213</v>
-      </c>
-      <c r="K11" t="n">
-        <v>500.0257683940144</v>
-      </c>
-      <c r="L11" t="n">
-        <v>18.10094816423416</v>
-      </c>
-      <c r="M11" t="n">
-        <v>499.9737119065001</v>
-      </c>
-      <c r="N11" t="n">
-        <v>19.45988489500999</v>
-      </c>
-      <c r="O11" t="n">
-        <v>498.8943192184187</v>
-      </c>
-      <c r="P11" t="n">
-        <v>15.81066906628722</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>497.1290974651837</v>
-      </c>
       <c r="R11" t="n">
-        <v>14.87007768023659</v>
+        <v>499.33</v>
       </c>
       <c r="S11" t="n">
-        <v>496.3246792402105</v>
+        <v>19.03</v>
       </c>
       <c r="T11" t="n">
-        <v>13.88862880395878</v>
+        <v>500.03</v>
       </c>
       <c r="U11" t="n">
-        <v>496.7949501530479</v>
+        <v>18.1</v>
       </c>
       <c r="V11" t="n">
-        <v>13.88171971234585</v>
+        <v>499.97</v>
       </c>
       <c r="W11" t="n">
-        <v>497.7594008273388</v>
+        <v>19.46</v>
       </c>
       <c r="X11" t="n">
-        <v>13.94570140381446</v>
+        <v>498.89</v>
       </c>
       <c r="Y11" t="n">
-        <v>498.5617361208063</v>
+        <v>15.81</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.19230230648839</v>
+        <v>497.13</v>
       </c>
       <c r="AA11" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>496.32</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>496.79</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>497.76</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>498.56</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>0.1794871794871795</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AK11" t="n">
         <v>0.1525423728813559</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AL11" t="n">
         <v>0.06329113924050633</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AM11" t="n">
         <v>0.0707070707070707</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AN11" t="n">
         <v>0.06779661016949153</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AO11" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AP11" t="n">
         <v>0.02531645569620253</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AQ11" t="n">
         <v>-0.005649717514124294</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AR11" t="n">
         <v>0.01522842639593909</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AS11" t="n">
         <v>506.05</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>504.1666666666667</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>502.4</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>502.27</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>501.7</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>500.9928571428571</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>500.4375</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>500.2</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>500.595</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>32.90968702373208</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>28.58272594106836</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>27.63946453895227</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>25.74406921991937</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>24.21177399531063</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>23.3973430813267</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>22.41893382277578</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>21.58816548224718</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>21.01049678137097</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>454</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>454</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>454</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>454</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>454</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>454</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>454</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>454</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>454</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BT11" t="n">
         <v>638</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BU11" t="n">
         <v>638</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BV11" t="n">
         <v>638</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BW11" t="n">
         <v>638</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BX11" t="n">
         <v>638</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BY11" t="n">
         <v>638</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BZ11" t="n">
         <v>638</v>
       </c>
-      <c r="BR11" t="n">
+      <c r="CA11" t="n">
         <v>638</v>
       </c>
-      <c r="BS11" t="n">
+      <c r="CB11" t="n">
         <v>638</v>
       </c>
-      <c r="BT11" t="n">
+      <c r="CC11" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.9545454545454546</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.04</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.03125</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>0.02777777777777778</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>498.56</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>14.19</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>502</v>
       </c>
       <c r="C12" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D12" t="n">
         <v>21</v>
-      </c>
-      <c r="D12" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E12" t="n">
         <v>502</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>502.5531205255165</v>
-      </c>
-      <c r="J12" t="n">
-        <v>20.68405557047766</v>
-      </c>
-      <c r="K12" t="n">
-        <v>499.0715980474253</v>
-      </c>
-      <c r="L12" t="n">
-        <v>21.6152420843997</v>
-      </c>
-      <c r="M12" t="n">
-        <v>500.4189388914514</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20.47709639678795</v>
-      </c>
-      <c r="O12" t="n">
-        <v>501.8974849758462</v>
-      </c>
-      <c r="P12" t="n">
-        <v>21.20145539650248</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>503.5216155144002</v>
-      </c>
       <c r="R12" t="n">
-        <v>21.88242197535373</v>
+        <v>502.55</v>
       </c>
       <c r="S12" t="n">
-        <v>504.1856571913116</v>
+        <v>20.68</v>
       </c>
       <c r="T12" t="n">
-        <v>22.68534563952922</v>
+        <v>499.07</v>
       </c>
       <c r="U12" t="n">
-        <v>502.7196679633374</v>
+        <v>21.62</v>
       </c>
       <c r="V12" t="n">
-        <v>22.3401464917555</v>
+        <v>500.42</v>
       </c>
       <c r="W12" t="n">
-        <v>501.9316048334376</v>
+        <v>20.48</v>
       </c>
       <c r="X12" t="n">
-        <v>21.2729033563347</v>
+        <v>501.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>501.7458961810356</v>
+        <v>21.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.52873158820908</v>
+        <v>503.52</v>
       </c>
       <c r="AA12" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>504.19</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>22.69</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>502.72</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>501.93</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>501.75</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>0.2</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AK12" t="n">
         <v>0.1</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AL12" t="n">
         <v>0.125</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AM12" t="n">
         <v>0.12</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AN12" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AO12" t="n">
         <v>0.1285714285714286</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AP12" t="n">
         <v>0.1125</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AQ12" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AR12" t="n">
         <v>0.09</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AS12" t="n">
         <v>509.95</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>504.2166666666666</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>504.0125</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>503.77</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>504.05</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>504.6714285714286</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>504.31875</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>503.8666666666667</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>503.92</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>34.38891536527432</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>31.36510357423075</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>28.75347533342709</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>27.717451181521</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>27.27509547798748</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>27.20174439184339</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>27.1926855686874</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>27.05065207675737</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>26.4265699628234</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>458</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>458</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>458</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>458</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>458</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>458</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>458</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>458</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>458</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BT12" t="n">
         <v>624</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BU12" t="n">
         <v>624</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BV12" t="n">
         <v>624</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BW12" t="n">
         <v>624</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BX12" t="n">
         <v>624</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BY12" t="n">
         <v>624</v>
       </c>
-      <c r="BQ12" t="n">
+      <c r="BZ12" t="n">
         <v>624</v>
       </c>
-      <c r="BR12" t="n">
+      <c r="CA12" t="n">
         <v>624</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="CB12" t="n">
         <v>624</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="CC12" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.875</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.7666666666666667</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>501.75</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>20.53</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>500</v>
       </c>
       <c r="C13" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D13" t="n">
         <v>22</v>
-      </c>
-      <c r="D13" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E13" t="n">
         <v>500</v>
@@ -3558,228 +3976,261 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>493.1729690889187</v>
-      </c>
-      <c r="J13" t="n">
-        <v>12.31865711887507</v>
-      </c>
-      <c r="K13" t="n">
-        <v>498.110977773547</v>
-      </c>
-      <c r="L13" t="n">
-        <v>19.08771651605302</v>
-      </c>
-      <c r="M13" t="n">
-        <v>497.4221054688092</v>
-      </c>
-      <c r="N13" t="n">
-        <v>24.10641502864947</v>
-      </c>
-      <c r="O13" t="n">
-        <v>496.8706333130922</v>
-      </c>
-      <c r="P13" t="n">
-        <v>29.01632807298442</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>497.8083139539857</v>
-      </c>
       <c r="R13" t="n">
-        <v>25.44896270336777</v>
+        <v>493.17</v>
       </c>
       <c r="S13" t="n">
-        <v>497.9152807693451</v>
+        <v>12.32</v>
       </c>
       <c r="T13" t="n">
-        <v>26.03771847690584</v>
+        <v>498.11</v>
       </c>
       <c r="U13" t="n">
-        <v>498.1950616489736</v>
+        <v>19.09</v>
       </c>
       <c r="V13" t="n">
-        <v>25.13751869333598</v>
+        <v>497.42</v>
       </c>
       <c r="W13" t="n">
-        <v>498.5682589632726</v>
+        <v>24.11</v>
       </c>
       <c r="X13" t="n">
-        <v>24.04899269197763</v>
+        <v>496.87</v>
       </c>
       <c r="Y13" t="n">
-        <v>500.6450862824934</v>
+        <v>29.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>23.36467902418318</v>
+        <v>497.81</v>
       </c>
       <c r="AA13" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>497.92</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>498.2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>498.57</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>500.65</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>-0.15</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AK13" t="n">
         <v>-0.05084745762711865</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AL13" t="n">
         <v>-0.06329113924050633</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AM13" t="n">
         <v>-0.0303030303030303</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AN13" t="n">
         <v>-0.008403361344537815</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AO13" t="n">
         <v>-0.007194244604316547</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AP13" t="n">
         <v>0.006289308176100629</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AQ13" t="n">
         <v>-0.00558659217877095</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AR13" t="n">
         <v>-0.01507537688442211</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AS13" t="n">
         <v>491.925</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>494.6166666666667</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>494.9375</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>495.86</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>496.8</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>497.0642857142857</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>497.3625</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>497.25</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>497.34</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>30.4986782500488</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>28.32848487927929</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>29.19518100217911</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>30.36215407378073</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>30.38574227056718</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>30.30492904611057</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>30.10740928326448</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>29.21640996274373</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>28.70077350874014</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>353</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>353</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>353</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>353</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>353</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>353</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>353</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>353</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>353</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BT13" t="n">
         <v>539</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BU13" t="n">
         <v>539</v>
       </c>
-      <c r="BM13" t="n">
+      <c r="BV13" t="n">
         <v>541</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BW13" t="n">
         <v>544</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BX13" t="n">
         <v>544</v>
       </c>
-      <c r="BP13" t="n">
+      <c r="BY13" t="n">
         <v>544</v>
       </c>
-      <c r="BQ13" t="n">
+      <c r="BZ13" t="n">
         <v>544</v>
       </c>
-      <c r="BR13" t="n">
+      <c r="CA13" t="n">
         <v>544</v>
       </c>
-      <c r="BS13" t="n">
+      <c r="CB13" t="n">
         <v>544</v>
       </c>
-      <c r="BT13" t="n">
+      <c r="CC13" t="n">
         <v>0.75</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.7391304347826086</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.7586206896551724</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.84375</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.9117647058823529</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.9210526315789473</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>500.65</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>23.36</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>501</v>
       </c>
       <c r="C14" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D14" t="n">
         <v>21</v>
-      </c>
-      <c r="D14" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E14" t="n">
         <v>501</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>486.332600938799</v>
-      </c>
-      <c r="J14" t="n">
-        <v>13.92372160729163</v>
-      </c>
-      <c r="K14" t="n">
-        <v>493.1927672104856</v>
-      </c>
-      <c r="L14" t="n">
-        <v>26.40993239125505</v>
-      </c>
-      <c r="M14" t="n">
-        <v>493.6955310828925</v>
-      </c>
-      <c r="N14" t="n">
-        <v>24.13599468502392</v>
-      </c>
-      <c r="O14" t="n">
-        <v>496.9443863135046</v>
-      </c>
-      <c r="P14" t="n">
-        <v>23.09233715125479</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>498.336668982881</v>
-      </c>
       <c r="R14" t="n">
-        <v>28.76562062418833</v>
+        <v>486.33</v>
       </c>
       <c r="S14" t="n">
-        <v>498.6351492689737</v>
+        <v>13.92</v>
       </c>
       <c r="T14" t="n">
-        <v>28.65184971797317</v>
+        <v>493.19</v>
       </c>
       <c r="U14" t="n">
-        <v>497.7597437941079</v>
+        <v>26.41</v>
       </c>
       <c r="V14" t="n">
-        <v>27.36140838279016</v>
+        <v>493.7</v>
       </c>
       <c r="W14" t="n">
-        <v>496.613799873329</v>
+        <v>24.14</v>
       </c>
       <c r="X14" t="n">
-        <v>27.02681751691166</v>
+        <v>496.94</v>
       </c>
       <c r="Y14" t="n">
-        <v>496.4748556302981</v>
+        <v>23.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.0123060697142</v>
+        <v>498.34</v>
       </c>
       <c r="AA14" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>498.64</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>497.76</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>496.61</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>496.47</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AK14" t="n">
         <v>-0.1333333333333333</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AL14" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AM14" t="n">
         <v>0</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AN14" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AO14" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AP14" t="n">
         <v>0.025</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AQ14" t="n">
         <v>0.01111111111111111</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AR14" t="n">
         <v>0.01</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AS14" t="n">
         <v>483.85</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>489.7</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>492.05</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>493.18</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>495.225</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>495.8571428571428</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>495.40625</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>495.2888888888889</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>495.24</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>28.78675910900704</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>28.89307875599276</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>29.7148531882626</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>29.02046863853167</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>29.8022545288104</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>30.6040546866801</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>30.3408340514479</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>29.85994881458902</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>29.51173325984091</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>358</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>358</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>358</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>358</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>358</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>358</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>358</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>358</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>358</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BT14" t="n">
         <v>543</v>
       </c>
-      <c r="BL14" t="n">
+      <c r="BU14" t="n">
         <v>543</v>
       </c>
-      <c r="BM14" t="n">
+      <c r="BV14" t="n">
         <v>543</v>
       </c>
-      <c r="BN14" t="n">
+      <c r="BW14" t="n">
         <v>543</v>
       </c>
-      <c r="BO14" t="n">
+      <c r="BX14" t="n">
         <v>546</v>
       </c>
-      <c r="BP14" t="n">
+      <c r="BY14" t="n">
         <v>546</v>
       </c>
-      <c r="BQ14" t="n">
+      <c r="BZ14" t="n">
         <v>546</v>
       </c>
-      <c r="BR14" t="n">
+      <c r="CA14" t="n">
         <v>546</v>
       </c>
-      <c r="BS14" t="n">
+      <c r="CB14" t="n">
         <v>546</v>
       </c>
-      <c r="BT14" t="n">
+      <c r="CC14" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.6842105263157895</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.7666666666666667</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>0.90625</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.8421052631578947</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>496.47</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>25.01</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>498</v>
       </c>
       <c r="C15" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D15" t="n">
         <v>22</v>
-      </c>
-      <c r="D15" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E15" t="n">
         <v>498</v>
@@ -4050,228 +4534,261 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>506.613890890237</v>
-      </c>
-      <c r="J15" t="n">
-        <v>30.61967439276998</v>
-      </c>
-      <c r="K15" t="n">
-        <v>502.0306956897455</v>
-      </c>
-      <c r="L15" t="n">
-        <v>31.55722905066568</v>
-      </c>
-      <c r="M15" t="n">
-        <v>503.2914663943082</v>
-      </c>
-      <c r="N15" t="n">
-        <v>30.68274975442792</v>
-      </c>
-      <c r="O15" t="n">
-        <v>499.8138656143541</v>
-      </c>
-      <c r="P15" t="n">
-        <v>28.94408955527242</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>500.5999711559023</v>
-      </c>
       <c r="R15" t="n">
-        <v>30.74213113818051</v>
+        <v>506.61</v>
       </c>
       <c r="S15" t="n">
-        <v>498.0309127378457</v>
+        <v>30.62</v>
       </c>
       <c r="T15" t="n">
-        <v>31.24171077516969</v>
+        <v>502.03</v>
       </c>
       <c r="U15" t="n">
-        <v>500.9113272809444</v>
+        <v>31.56</v>
       </c>
       <c r="V15" t="n">
-        <v>30.42546369963151</v>
+        <v>503.29</v>
       </c>
       <c r="W15" t="n">
-        <v>500.0430485013378</v>
+        <v>30.68</v>
       </c>
       <c r="X15" t="n">
-        <v>30.30528126489062</v>
+        <v>499.81</v>
       </c>
       <c r="Y15" t="n">
-        <v>500.0170900672991</v>
+        <v>28.94</v>
       </c>
       <c r="Z15" t="n">
-        <v>29.79073067755197</v>
+        <v>500.6</v>
       </c>
       <c r="AA15" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>498.03</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>500.91</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>500.04</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>30.31</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>500.02</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>29.79</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>0.15</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AK15" t="n">
         <v>-0.03333333333333333</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AL15" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AM15" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AN15" t="n">
         <v>0</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AO15" t="n">
         <v>-0.02857142857142857</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AP15" t="n">
         <v>0</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AQ15" t="n">
         <v>-0.02222222222222222</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AR15" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AS15" t="n">
         <v>511.15</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>503.6166666666667</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>502.95</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>503.75</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>504.725</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>502.8142857142857</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>503.075</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>502.1833333333333</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>502.585</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>33.88255450818311</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>38.09728409684285</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>36.9096532088829</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>35.60768877644265</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>35.57432653379868</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>35.11706661079395</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>34.83363137831024</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>34.45552285999381</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>33.85591196526834</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>454</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>442</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>442</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>442</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>442</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>442</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>442</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>442</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>442</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BT15" t="n">
         <v>627</v>
       </c>
-      <c r="BL15" t="n">
+      <c r="BU15" t="n">
         <v>627</v>
       </c>
-      <c r="BM15" t="n">
+      <c r="BV15" t="n">
         <v>627</v>
       </c>
-      <c r="BN15" t="n">
+      <c r="BW15" t="n">
         <v>627</v>
       </c>
-      <c r="BO15" t="n">
+      <c r="BX15" t="n">
         <v>627</v>
       </c>
-      <c r="BP15" t="n">
+      <c r="BY15" t="n">
         <v>627</v>
       </c>
-      <c r="BQ15" t="n">
+      <c r="BZ15" t="n">
         <v>627</v>
       </c>
-      <c r="BR15" t="n">
+      <c r="CA15" t="n">
         <v>627</v>
       </c>
-      <c r="BS15" t="n">
+      <c r="CB15" t="n">
         <v>627</v>
       </c>
-      <c r="BT15" t="n">
+      <c r="CC15" t="n">
         <v>1</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>1</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>1</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.9259259259259259</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.9354838709677419</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>500.02</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>29.79</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>502</v>
       </c>
       <c r="C16" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D16" t="n">
         <v>22</v>
-      </c>
-      <c r="D16" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E16" t="n">
         <v>502</v>
@@ -4296,244 +4813,277 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>491.9392769198578</v>
-      </c>
-      <c r="J16" t="n">
-        <v>26.73011757444748</v>
-      </c>
-      <c r="K16" t="n">
-        <v>496.971989962335</v>
-      </c>
-      <c r="L16" t="n">
-        <v>29.31970937341237</v>
-      </c>
-      <c r="M16" t="n">
-        <v>497.3575810370769</v>
-      </c>
-      <c r="N16" t="n">
-        <v>26.10708110062222</v>
-      </c>
-      <c r="O16" t="n">
-        <v>495.7757916089923</v>
-      </c>
-      <c r="P16" t="n">
-        <v>28.09423626995419</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>494.7918981265717</v>
-      </c>
       <c r="R16" t="n">
-        <v>28.98548347784295</v>
+        <v>491.94</v>
       </c>
       <c r="S16" t="n">
-        <v>496.4168892174266</v>
+        <v>26.73</v>
       </c>
       <c r="T16" t="n">
-        <v>27.65511256376331</v>
+        <v>496.97</v>
       </c>
       <c r="U16" t="n">
-        <v>497.8988577138065</v>
+        <v>29.32</v>
       </c>
       <c r="V16" t="n">
-        <v>27.05416412406064</v>
+        <v>497.36</v>
       </c>
       <c r="W16" t="n">
-        <v>498.9825578972221</v>
+        <v>26.11</v>
       </c>
       <c r="X16" t="n">
-        <v>27.60379490921354</v>
+        <v>495.78</v>
       </c>
       <c r="Y16" t="n">
-        <v>497.1883397628621</v>
+        <v>28.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>26.52194365220864</v>
+        <v>494.79</v>
       </c>
       <c r="AA16" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>496.42</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>497.9</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>498.98</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>497.19</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>-0.05</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
         <v>-0.03333333333333333</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AL16" t="n">
         <v>-0.075</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AM16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AN16" t="n">
         <v>-0.03333333333333333</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AO16" t="n">
         <v>0</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AP16" t="n">
         <v>0.0125</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AQ16" t="n">
         <v>0.02222222222222222</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AR16" t="n">
         <v>0.01</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AS16" t="n">
         <v>496.325</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>495.2833333333334</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>494.875</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>494.97</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>495.2416666666667</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>495.6642857142857</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>495.60625</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>496.15</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>495.945</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>43.53928542132955</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>39.59044146704549</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>36.59725911868264</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>34.5865450717472</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>33.62588185543326</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>32.92038246485987</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>32.02344783026181</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>31.6158320044457</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>31.22854423440196</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>430</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>430</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>430</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>430</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>430</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>430</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>430</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>430</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>430</v>
       </c>
-      <c r="BK16" t="n">
+      <c r="BT16" t="n">
         <v>631</v>
       </c>
-      <c r="BL16" t="n">
+      <c r="BU16" t="n">
         <v>631</v>
       </c>
-      <c r="BM16" t="n">
+      <c r="BV16" t="n">
         <v>631</v>
       </c>
-      <c r="BN16" t="n">
+      <c r="BW16" t="n">
         <v>631</v>
       </c>
-      <c r="BO16" t="n">
+      <c r="BX16" t="n">
         <v>631</v>
       </c>
-      <c r="BP16" t="n">
+      <c r="BY16" t="n">
         <v>631</v>
       </c>
-      <c r="BQ16" t="n">
+      <c r="BZ16" t="n">
         <v>631</v>
       </c>
-      <c r="BR16" t="n">
+      <c r="CA16" t="n">
         <v>631</v>
       </c>
-      <c r="BS16" t="n">
+      <c r="CB16" t="n">
         <v>631</v>
       </c>
-      <c r="BT16" t="n">
+      <c r="CC16" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>1</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.75</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.3888888888888889</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.9615384615384616</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.9487179487179487</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>497.19</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>26.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S17_G4_499_19_ABS1</t>
+          <t>S16_G4_499_19_ABS1</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>499</v>
       </c>
       <c r="C17" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D17" t="n">
         <v>19</v>
-      </c>
-      <c r="D17" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E17" t="n">
         <v>499</v>
@@ -4542,244 +5092,277 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>494.5924689376957</v>
-      </c>
-      <c r="J17" t="n">
-        <v>10.32608474219045</v>
-      </c>
-      <c r="K17" t="n">
-        <v>501.4661147278634</v>
-      </c>
-      <c r="L17" t="n">
-        <v>18.16632912875464</v>
-      </c>
-      <c r="M17" t="n">
-        <v>500.1914120180989</v>
-      </c>
-      <c r="N17" t="n">
-        <v>16.02787665096313</v>
-      </c>
-      <c r="O17" t="n">
-        <v>502.2658481502029</v>
-      </c>
-      <c r="P17" t="n">
-        <v>19.244437435175</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>501.9172414367118</v>
-      </c>
       <c r="R17" t="n">
-        <v>18.52447125770322</v>
+        <v>502.76</v>
       </c>
       <c r="S17" t="n">
-        <v>500.0044408981794</v>
+        <v>12.24</v>
       </c>
       <c r="T17" t="n">
-        <v>21.06069918325896</v>
+        <v>501.07</v>
       </c>
       <c r="U17" t="n">
-        <v>500.1750501405596</v>
+        <v>11.92</v>
       </c>
       <c r="V17" t="n">
-        <v>20.51243111977396</v>
+        <v>500.64</v>
       </c>
       <c r="W17" t="n">
-        <v>497.9460106472852</v>
+        <v>12.55</v>
       </c>
       <c r="X17" t="n">
-        <v>22.47715969242752</v>
+        <v>499.91</v>
       </c>
       <c r="Y17" t="n">
-        <v>497.7918101073705</v>
+        <v>14.63</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.26905006599866</v>
+        <v>502.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.282051282051282</v>
+        <v>17.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0847457627118644</v>
+        <v>499.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0379746835443038</v>
+        <v>20.68</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.1111111111111111</v>
+        <v>498.72</v>
       </c>
       <c r="AE17" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>498.31</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>497.97</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.07692307692307693</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.05084745762711865</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.01265822784810127</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="AN17" t="n">
         <v>0.1092436974789916</v>
       </c>
-      <c r="AF17" t="n">
-        <v>0.02158273381294964</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0.01886792452830189</v>
-      </c>
-      <c r="AH17" t="n">
+      <c r="AO17" t="n">
+        <v>0.007194244604316547</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-0.03144654088050314</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>-0.03910614525139665</v>
       </c>
-      <c r="AI17" t="n">
-        <v>-0.05527638190954774</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>490.325</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>499.8</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>500.0125</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>501.84</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>502.1666666666667</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>500.6428571428572</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>500.7</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>499.1833333333333</v>
-      </c>
       <c r="AR17" t="n">
-        <v>498.995</v>
+        <v>-0.02512562814070352</v>
       </c>
       <c r="AS17" t="n">
-        <v>30.75336363716983</v>
+        <v>499.575</v>
       </c>
       <c r="AT17" t="n">
-        <v>30.05927477501744</v>
+        <v>501.0166666666667</v>
       </c>
       <c r="AU17" t="n">
-        <v>27.63896423077392</v>
+        <v>500.85</v>
       </c>
       <c r="AV17" t="n">
-        <v>27.14911416602759</v>
+        <v>500.74</v>
       </c>
       <c r="AW17" t="n">
-        <v>26.46423162601846</v>
+        <v>502.9833333333333</v>
       </c>
       <c r="AX17" t="n">
-        <v>25.70632813379711</v>
+        <v>500.5928571428572</v>
       </c>
       <c r="AY17" t="n">
-        <v>25.47297587640675</v>
+        <v>499.3125</v>
       </c>
       <c r="AZ17" t="n">
-        <v>25.45332874978132</v>
+        <v>498.8611111111111</v>
       </c>
       <c r="BA17" t="n">
-        <v>25.26964532794238</v>
+        <v>498.865</v>
       </c>
       <c r="BB17" t="n">
-        <v>350</v>
+        <v>29.58283919775112</v>
       </c>
       <c r="BC17" t="n">
-        <v>350</v>
+        <v>25.2715199824273</v>
       </c>
       <c r="BD17" t="n">
-        <v>350</v>
+        <v>23.36883608569327</v>
       </c>
       <c r="BE17" t="n">
-        <v>350</v>
+        <v>22.32515173520664</v>
       </c>
       <c r="BF17" t="n">
-        <v>350</v>
+        <v>22.06127199918949</v>
       </c>
       <c r="BG17" t="n">
-        <v>350</v>
+        <v>22.45213843731067</v>
       </c>
       <c r="BH17" t="n">
-        <v>350</v>
+        <v>22.8457292234238</v>
       </c>
       <c r="BI17" t="n">
-        <v>350</v>
+        <v>22.95472933330803</v>
       </c>
       <c r="BJ17" t="n">
-        <v>350</v>
+        <v>22.95118243141298</v>
       </c>
       <c r="BK17" t="n">
-        <v>570</v>
+        <v>453</v>
       </c>
       <c r="BL17" t="n">
-        <v>570</v>
+        <v>453</v>
       </c>
       <c r="BM17" t="n">
-        <v>570</v>
+        <v>453</v>
       </c>
       <c r="BN17" t="n">
-        <v>570</v>
+        <v>453</v>
       </c>
       <c r="BO17" t="n">
-        <v>570</v>
+        <v>453</v>
       </c>
       <c r="BP17" t="n">
-        <v>570</v>
+        <v>453</v>
       </c>
       <c r="BQ17" t="n">
-        <v>570</v>
+        <v>453</v>
       </c>
       <c r="BR17" t="n">
-        <v>570</v>
+        <v>453</v>
       </c>
       <c r="BS17" t="n">
-        <v>570</v>
+        <v>453</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.09090909090909091</v>
+        <v>620</v>
       </c>
       <c r="BU17" t="n">
-        <v>1</v>
+        <v>620</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.7894736842105263</v>
+        <v>620</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.9047619047619048</v>
+        <v>620</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.92</v>
+        <v>620</v>
       </c>
       <c r="BY17" t="n">
+        <v>620</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>620</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>620</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>620</v>
+      </c>
+      <c r="CC17" t="n">
         <v>0.75</v>
       </c>
-      <c r="BZ17" t="n">
-        <v>0.6842105263157895</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>0.6279069767441861</v>
-      </c>
-      <c r="CB17" t="n">
-        <v>0.6530612244897959</v>
+      <c r="CD17" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>497.97</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>20.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S16_G4_499_19_ABS1</t>
+          <t>S17_G4_499_19_ABS1</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>499</v>
       </c>
       <c r="C18" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D18" t="n">
         <v>19</v>
-      </c>
-      <c r="D18" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E18" t="n">
         <v>499</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>502.7608951540917</v>
-      </c>
-      <c r="J18" t="n">
-        <v>12.24352763602925</v>
-      </c>
-      <c r="K18" t="n">
-        <v>501.0716069709925</v>
-      </c>
-      <c r="L18" t="n">
-        <v>11.92154094198417</v>
-      </c>
-      <c r="M18" t="n">
-        <v>500.6422128935847</v>
-      </c>
-      <c r="N18" t="n">
-        <v>12.55448779856321</v>
-      </c>
-      <c r="O18" t="n">
-        <v>499.9120592488144</v>
-      </c>
-      <c r="P18" t="n">
-        <v>14.634061835234</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>502.6007136178402</v>
-      </c>
       <c r="R18" t="n">
-        <v>17.20368204876607</v>
+        <v>494.59</v>
       </c>
       <c r="S18" t="n">
-        <v>499.4011908650794</v>
+        <v>10.33</v>
       </c>
       <c r="T18" t="n">
-        <v>20.68183087209559</v>
+        <v>501.47</v>
       </c>
       <c r="U18" t="n">
-        <v>498.7187189901844</v>
+        <v>18.17</v>
       </c>
       <c r="V18" t="n">
-        <v>20.37544617178599</v>
+        <v>500.19</v>
       </c>
       <c r="W18" t="n">
-        <v>498.3108255660488</v>
+        <v>16.03</v>
       </c>
       <c r="X18" t="n">
-        <v>21.32258678124985</v>
+        <v>502.27</v>
       </c>
       <c r="Y18" t="n">
-        <v>497.9671773497583</v>
+        <v>19.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.41481445849865</v>
+        <v>501.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.07692307692307693</v>
+        <v>18.52</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.05084745762711865</v>
+        <v>500</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.01265822784810127</v>
+        <v>21.06</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0101010101010101</v>
+        <v>500.18</v>
       </c>
       <c r="AE18" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>497.95</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>497.79</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.282051282051282</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.0847457627118644</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.0379746835443038</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AN18" t="n">
         <v>0.1092436974789916</v>
       </c>
-      <c r="AF18" t="n">
-        <v>0.007194244604316547</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>-0.03144654088050314</v>
-      </c>
-      <c r="AH18" t="n">
+      <c r="AO18" t="n">
+        <v>0.02158273381294964</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.01886792452830189</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>-0.03910614525139665</v>
       </c>
-      <c r="AI18" t="n">
-        <v>-0.02512562814070352</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>499.575</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>501.0166666666667</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>500.85</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>500.74</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>502.9833333333333</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>500.5928571428572</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>499.3125</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>498.8611111111111</v>
-      </c>
       <c r="AR18" t="n">
-        <v>498.865</v>
+        <v>-0.05527638190954774</v>
       </c>
       <c r="AS18" t="n">
-        <v>29.58283919775112</v>
+        <v>490.325</v>
       </c>
       <c r="AT18" t="n">
-        <v>25.2715199824273</v>
+        <v>499.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>23.36883608569327</v>
+        <v>500.0125</v>
       </c>
       <c r="AV18" t="n">
-        <v>22.32515173520664</v>
+        <v>501.84</v>
       </c>
       <c r="AW18" t="n">
-        <v>22.06127199918949</v>
+        <v>502.1666666666667</v>
       </c>
       <c r="AX18" t="n">
-        <v>22.45213843731067</v>
+        <v>500.6428571428572</v>
       </c>
       <c r="AY18" t="n">
-        <v>22.8457292234238</v>
+        <v>500.7</v>
       </c>
       <c r="AZ18" t="n">
-        <v>22.95472933330803</v>
+        <v>499.1833333333333</v>
       </c>
       <c r="BA18" t="n">
-        <v>22.95118243141298</v>
+        <v>498.995</v>
       </c>
       <c r="BB18" t="n">
-        <v>453</v>
+        <v>30.75336363716983</v>
       </c>
       <c r="BC18" t="n">
-        <v>453</v>
+        <v>30.05927477501744</v>
       </c>
       <c r="BD18" t="n">
-        <v>453</v>
+        <v>27.63896423077392</v>
       </c>
       <c r="BE18" t="n">
-        <v>453</v>
+        <v>27.14911416602759</v>
       </c>
       <c r="BF18" t="n">
-        <v>453</v>
+        <v>26.46423162601846</v>
       </c>
       <c r="BG18" t="n">
-        <v>453</v>
+        <v>25.70632813379711</v>
       </c>
       <c r="BH18" t="n">
-        <v>453</v>
+        <v>25.47297587640675</v>
       </c>
       <c r="BI18" t="n">
-        <v>453</v>
+        <v>25.45332874978132</v>
       </c>
       <c r="BJ18" t="n">
-        <v>453</v>
+        <v>25.26964532794238</v>
       </c>
       <c r="BK18" t="n">
-        <v>620</v>
+        <v>350</v>
       </c>
       <c r="BL18" t="n">
-        <v>620</v>
+        <v>350</v>
       </c>
       <c r="BM18" t="n">
-        <v>620</v>
+        <v>350</v>
       </c>
       <c r="BN18" t="n">
-        <v>620</v>
+        <v>350</v>
       </c>
       <c r="BO18" t="n">
-        <v>620</v>
+        <v>350</v>
       </c>
       <c r="BP18" t="n">
-        <v>620</v>
+        <v>350</v>
       </c>
       <c r="BQ18" t="n">
-        <v>620</v>
+        <v>350</v>
       </c>
       <c r="BR18" t="n">
-        <v>620</v>
+        <v>350</v>
       </c>
       <c r="BS18" t="n">
-        <v>620</v>
+        <v>350</v>
       </c>
       <c r="BT18" t="n">
+        <v>570</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>570</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>570</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>570</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>570</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>570</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>570</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>570</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>570</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CH18" t="n">
         <v>0.75</v>
       </c>
-      <c r="BU18" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>0.9615384615384616</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>0.8620689655172413</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>0.9117647058823529</v>
+      <c r="CI18" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0.6279069767441861</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.6530612244897959</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>497.79</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>21.27</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>499</v>
       </c>
       <c r="C19" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D19" t="n">
         <v>21</v>
-      </c>
-      <c r="D19" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E19" t="n">
         <v>499</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>71.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>512.7246927525731</v>
-      </c>
-      <c r="J19" t="n">
-        <v>26.40019637848047</v>
-      </c>
-      <c r="K19" t="n">
-        <v>507.7703383099684</v>
-      </c>
-      <c r="L19" t="n">
-        <v>25.52618219843052</v>
-      </c>
-      <c r="M19" t="n">
-        <v>506.9444739220852</v>
-      </c>
-      <c r="N19" t="n">
-        <v>21.81494348130644</v>
-      </c>
-      <c r="O19" t="n">
-        <v>504.3888182194256</v>
-      </c>
-      <c r="P19" t="n">
-        <v>22.30875548151499</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>503.1515280352021</v>
-      </c>
       <c r="R19" t="n">
-        <v>21.96199870757757</v>
+        <v>512.72</v>
       </c>
       <c r="S19" t="n">
-        <v>504.0393776977423</v>
+        <v>26.4</v>
       </c>
       <c r="T19" t="n">
-        <v>21.4585529463134</v>
+        <v>507.77</v>
       </c>
       <c r="U19" t="n">
-        <v>502.1830641127127</v>
+        <v>25.53</v>
       </c>
       <c r="V19" t="n">
-        <v>24.00216610131374</v>
+        <v>506.94</v>
       </c>
       <c r="W19" t="n">
-        <v>500.4188555160345</v>
+        <v>21.81</v>
       </c>
       <c r="X19" t="n">
-        <v>25.80340618651526</v>
+        <v>504.39</v>
       </c>
       <c r="Y19" t="n">
-        <v>501.2549728941735</v>
+        <v>22.31</v>
       </c>
       <c r="Z19" t="n">
-        <v>27.43432203349262</v>
+        <v>503.15</v>
       </c>
       <c r="AA19" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>504.04</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>502.18</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>500.42</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>501.25</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>0.4</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AK19" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AL19" t="n">
         <v>0.075</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AM19" t="n">
         <v>0.04</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AN19" t="n">
         <v>0.02521008403361345</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AO19" t="n">
         <v>0.02158273381294964</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AP19" t="n">
         <v>-0.01886792452830189</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AQ19" t="n">
         <v>-0.05027932960893855</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AR19" t="n">
         <v>-0.02512562814070352</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AS19" t="n">
         <v>513.7</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>509.3166666666667</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>508.425</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>507.84</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>507.025</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>506.6142857142857</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>505.3</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>503.9944444444445</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>504.385</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>34.52042873430167</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>34.05216178485916</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>32.65799098230018</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>31.09492563104147</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>29.72525932042758</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>28.7493070014083</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>28.0926591834949</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>28.18204653522487</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>27.97582483145046</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>459</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>456</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>456</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>456</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>456</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>456</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>456</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>456</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>456</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BT19" t="n">
         <v>643</v>
       </c>
-      <c r="BL19" t="n">
+      <c r="BU19" t="n">
         <v>643</v>
       </c>
-      <c r="BM19" t="n">
+      <c r="BV19" t="n">
         <v>643</v>
       </c>
-      <c r="BN19" t="n">
+      <c r="BW19" t="n">
         <v>643</v>
       </c>
-      <c r="BO19" t="n">
+      <c r="BX19" t="n">
         <v>643</v>
       </c>
-      <c r="BP19" t="n">
+      <c r="BY19" t="n">
         <v>643</v>
       </c>
-      <c r="BQ19" t="n">
+      <c r="BZ19" t="n">
         <v>643</v>
       </c>
-      <c r="BR19" t="n">
+      <c r="CA19" t="n">
         <v>643</v>
       </c>
-      <c r="BS19" t="n">
+      <c r="CB19" t="n">
         <v>643</v>
       </c>
-      <c r="BT19" t="n">
+      <c r="CC19" t="n">
         <v>0.375</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.7931034482758621</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.21875</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>501.25</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>27.43</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>502</v>
       </c>
       <c r="C20" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D20" t="n">
         <v>22</v>
-      </c>
-      <c r="D20" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E20" t="n">
         <v>502</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>73</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>510.9968071548465</v>
-      </c>
-      <c r="J20" t="n">
-        <v>11.35590281081934</v>
-      </c>
-      <c r="K20" t="n">
-        <v>505.8371109986737</v>
-      </c>
-      <c r="L20" t="n">
-        <v>20.51066779486795</v>
-      </c>
-      <c r="M20" t="n">
-        <v>503.2040825620247</v>
-      </c>
-      <c r="N20" t="n">
-        <v>18.13677096494201</v>
-      </c>
-      <c r="O20" t="n">
-        <v>503.3440986655809</v>
-      </c>
-      <c r="P20" t="n">
-        <v>17.14847391664962</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>505.9682166034676</v>
-      </c>
       <c r="R20" t="n">
-        <v>18.1143441936601</v>
+        <v>511</v>
       </c>
       <c r="S20" t="n">
-        <v>505.7210935384037</v>
+        <v>11.36</v>
       </c>
       <c r="T20" t="n">
-        <v>16.91324903634912</v>
+        <v>505.84</v>
       </c>
       <c r="U20" t="n">
-        <v>505.1660798511605</v>
+        <v>20.51</v>
       </c>
       <c r="V20" t="n">
-        <v>17.36662680938739</v>
+        <v>503.2</v>
       </c>
       <c r="W20" t="n">
-        <v>504.7723927060831</v>
+        <v>18.14</v>
       </c>
       <c r="X20" t="n">
-        <v>16.61356386468361</v>
+        <v>503.34</v>
       </c>
       <c r="Y20" t="n">
-        <v>503.8863739062217</v>
+        <v>17.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.93324535688402</v>
+        <v>505.97</v>
       </c>
       <c r="AA20" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>505.72</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>505.17</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>504.77</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>503.89</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>0.4210526315789473</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AK20" t="n">
         <v>0.1379310344827586</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AL20" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AM20" t="n">
         <v>0.04081632653061224</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AN20" t="n">
         <v>0.06779661016949153</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AO20" t="n">
         <v>0.07246376811594203</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AP20" t="n">
         <v>0.08860759493670886</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AQ20" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AR20" t="n">
         <v>0.06122448979591837</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AS20" t="n">
         <v>507.45</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>502.9166666666667</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>502.4375</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>502.78</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>503.85</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>503.9928571428571</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>504.54375</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>504.3</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>503.96</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>31.69144206248747</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>28.50631021760309</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>26.13706360228708</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>25.65914262012665</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>24.5202807216122</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>23.28564745827395</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>22.84098478475698</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>22.07912538525423</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>22.06871994475438</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>362</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>362</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>362</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>362</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>362</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>362</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>362</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>362</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>362</v>
       </c>
-      <c r="BK20" t="n">
+      <c r="BT20" t="n">
         <v>551</v>
       </c>
-      <c r="BL20" t="n">
+      <c r="BU20" t="n">
         <v>551</v>
       </c>
-      <c r="BM20" t="n">
+      <c r="BV20" t="n">
         <v>551</v>
       </c>
-      <c r="BN20" t="n">
+      <c r="BW20" t="n">
         <v>551</v>
       </c>
-      <c r="BO20" t="n">
+      <c r="BX20" t="n">
         <v>551</v>
       </c>
-      <c r="BP20" t="n">
+      <c r="BY20" t="n">
         <v>551</v>
       </c>
-      <c r="BQ20" t="n">
+      <c r="BZ20" t="n">
         <v>551</v>
       </c>
-      <c r="BR20" t="n">
+      <c r="CA20" t="n">
         <v>551</v>
       </c>
-      <c r="BS20" t="n">
+      <c r="CB20" t="n">
         <v>551</v>
       </c>
-      <c r="BT20" t="n">
+      <c r="CC20" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.9047619047619048</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.88</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.8518518518518519</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.9</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>1</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.9428571428571428</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>503.89</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>18.93</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>498</v>
       </c>
       <c r="C21" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D21" t="n">
         <v>19</v>
-      </c>
-      <c r="D21" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E21" t="n">
         <v>498</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>73</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>503.0398052124528</v>
-      </c>
-      <c r="J21" t="n">
-        <v>14.29228213582976</v>
-      </c>
-      <c r="K21" t="n">
-        <v>499.0566564660875</v>
-      </c>
-      <c r="L21" t="n">
-        <v>16.09116368055701</v>
-      </c>
-      <c r="M21" t="n">
-        <v>501.374001206591</v>
-      </c>
-      <c r="N21" t="n">
-        <v>18.35697468120595</v>
-      </c>
-      <c r="O21" t="n">
-        <v>499.7564634135302</v>
-      </c>
-      <c r="P21" t="n">
-        <v>19.92485154554842</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>501.9437463242055</v>
-      </c>
       <c r="R21" t="n">
-        <v>20.78684259271821</v>
+        <v>503.04</v>
       </c>
       <c r="S21" t="n">
-        <v>501.1723264339565</v>
+        <v>14.29</v>
       </c>
       <c r="T21" t="n">
-        <v>20.43080438689664</v>
+        <v>499.06</v>
       </c>
       <c r="U21" t="n">
-        <v>501.1522335222519</v>
+        <v>16.09</v>
       </c>
       <c r="V21" t="n">
-        <v>20.90197721751526</v>
+        <v>501.37</v>
       </c>
       <c r="W21" t="n">
-        <v>502.375261476203</v>
+        <v>18.36</v>
       </c>
       <c r="X21" t="n">
-        <v>21.44476062974469</v>
+        <v>499.76</v>
       </c>
       <c r="Y21" t="n">
-        <v>501.8091756239278</v>
+        <v>19.92</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.29175757454404</v>
+        <v>501.94</v>
       </c>
       <c r="AA21" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>501.17</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>501.15</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>502.38</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>501.81</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>-0.02564102564102564</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AK21" t="n">
         <v>-0.01694915254237288</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AL21" t="n">
         <v>0.06329113924050633</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AM21" t="n">
         <v>-0.0303030303030303</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AN21" t="n">
         <v>0.008403361344537815</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AO21" t="n">
         <v>0.02158273381294964</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AP21" t="n">
         <v>0.006289308176100629</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AQ21" t="n">
         <v>0.01675977653631285</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AR21" t="n">
         <v>0.01507537688442211</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AS21" t="n">
         <v>497.3</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>498.2</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>499.9125</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>497.98</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>499.6666666666667</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>500.45</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>500.6375</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>500.8666666666667</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>500.89</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>26.10287340504872</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>23.60776708345511</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>23.63217814231265</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>23.90814923828275</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>23.89397878592476</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>23.76561892434411</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>23.75091774542618</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>23.43605958536735</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>23.59995550843264</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>366</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>366</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>366</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>366</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>366</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>366</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>366</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>366</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>366</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BT21" t="n">
         <v>534</v>
       </c>
-      <c r="BL21" t="n">
+      <c r="BU21" t="n">
         <v>534</v>
       </c>
-      <c r="BM21" t="n">
+      <c r="BV21" t="n">
         <v>537</v>
       </c>
-      <c r="BN21" t="n">
+      <c r="BW21" t="n">
         <v>537</v>
       </c>
-      <c r="BO21" t="n">
+      <c r="BX21" t="n">
         <v>537</v>
       </c>
-      <c r="BP21" t="n">
+      <c r="BY21" t="n">
         <v>539</v>
       </c>
-      <c r="BQ21" t="n">
+      <c r="BZ21" t="n">
         <v>539</v>
       </c>
-      <c r="BR21" t="n">
+      <c r="CA21" t="n">
         <v>539</v>
       </c>
-      <c r="BS21" t="n">
+      <c r="CB21" t="n">
         <v>539</v>
       </c>
-      <c r="BT21" t="n">
+      <c r="CC21" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.9</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.9545454545454546</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.9565217391304348</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>1</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.9310344827586207</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>501.81</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>21.29</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>500</v>
       </c>
       <c r="C22" t="n">
+        <v>30.39288361749444</v>
+      </c>
+      <c r="D22" t="n">
         <v>20.5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>30.39288361749444</v>
       </c>
       <c r="E22" t="n">
         <v>500</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5025000000000001</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>75.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.3665</v>
+      </c>
       <c r="I22" t="n">
-        <v>500.5626455007804</v>
+        <v>2.338</v>
       </c>
       <c r="J22" t="n">
-        <v>19.98416715489483</v>
+        <v>2.319999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>500.4733794903062</v>
+        <v>2.2965</v>
       </c>
       <c r="L22" t="n">
-        <v>21.5803640173308</v>
+        <v>2.2785</v>
       </c>
       <c r="M22" t="n">
-        <v>500.3115303563341</v>
+        <v>2.2625</v>
       </c>
       <c r="N22" t="n">
-        <v>22.51737681621369</v>
+        <v>2.319</v>
       </c>
       <c r="O22" t="n">
-        <v>500.1479307849982</v>
+        <v>2.385</v>
       </c>
       <c r="P22" t="n">
-        <v>22.66468883274792</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>500.4269807526795</v>
-      </c>
+        <v>2.387</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>23.05205184589988</v>
+        <v>500.562</v>
       </c>
       <c r="S22" t="n">
-        <v>500.1595670975159</v>
+        <v>19.9835</v>
       </c>
       <c r="T22" t="n">
-        <v>23.16704796562653</v>
+        <v>500.4734999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>500.3661688528147</v>
+        <v>21.581</v>
       </c>
       <c r="V22" t="n">
-        <v>22.79262124127962</v>
+        <v>500.3105000000002</v>
       </c>
       <c r="W22" t="n">
-        <v>500.0912953057428</v>
+        <v>22.5175</v>
       </c>
       <c r="X22" t="n">
-        <v>23.01305399923936</v>
+        <v>500.148</v>
       </c>
       <c r="Y22" t="n">
-        <v>499.7666270794745</v>
+        <v>22.6635</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.76633850607509</v>
+        <v>500.4264999999999</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.06053981106612686</v>
+        <v>23.052</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.05774400935125658</v>
+        <v>500.16</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.03117494320025966</v>
+        <v>23.167</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.02631436817151103</v>
+        <v>500.366</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.03704647960879266</v>
+        <v>22.793</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.02597241461489194</v>
+        <v>500.091</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.02270932847703208</v>
+        <v>23.0125</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.009617309263559141</v>
+        <v>499.767</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.005614382269671042</v>
+        <v>22.7655</v>
       </c>
       <c r="AJ22" t="n">
-        <v>499.5387500000001</v>
+        <v>0.0605</v>
       </c>
       <c r="AK22" t="n">
-        <v>499.75</v>
+        <v>0.05800000000000001</v>
       </c>
       <c r="AL22" t="n">
-        <v>499.88625</v>
+        <v>0.03000000000000001</v>
       </c>
       <c r="AM22" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.009499999999999998</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.005500000000000001</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>499.539</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>499.751</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>499.8865000000001</v>
+      </c>
+      <c r="AV22" t="n">
         <v>499.956</v>
       </c>
-      <c r="AN22" t="n">
-        <v>500.4879166666666</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>500.2560714285715</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>500.2415625</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>499.9658333333333</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>499.9285</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>33.65934898188412</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>31.89104798682736</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>30.8351247068293</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>29.96643679834643</v>
-      </c>
       <c r="AW22" t="n">
-        <v>29.22656561292279</v>
+        <v>500.4895</v>
       </c>
       <c r="AX22" t="n">
-        <v>28.66699541808374</v>
+        <v>500.255</v>
       </c>
       <c r="AY22" t="n">
-        <v>28.15005016078928</v>
+        <v>500.2415</v>
       </c>
       <c r="AZ22" t="n">
-        <v>27.74578964069548</v>
+        <v>499.966</v>
       </c>
       <c r="BA22" t="n">
-        <v>27.36287476909335</v>
+        <v>499.9284999999999</v>
       </c>
       <c r="BB22" t="n">
+        <v>33.6595</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>31.8915</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>30.836</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>29.967</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>29.227</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>28.66699999999999</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>28.14900000000001</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>27.7465</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>27.36300000000001</v>
+      </c>
+      <c r="BK22" t="n">
         <v>396.25</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>395.05</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>394.7</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>394.7</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>394.7</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>394.7</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>394.7</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>394.7</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>394.7</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>592.45</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>593.9</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>594.7</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>595.5</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>595.65</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>595.75</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>595.75</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>595.75</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>595.75</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.5285722610722611</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.7301344488844489</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7394672651909493</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.6896804824862101</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.7637905974862497</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.8146730625491772</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.747372493378909</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.8270706421676268</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.7874451172832005</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>499.767</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>22.7655</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.486783883350056</v>
       </c>
       <c r="C23" t="n">
+        <v>2.068912423793508</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.395481429848721</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.068912423793508</v>
       </c>
       <c r="E23" t="n">
         <v>1.486783883350056</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01568606488508025</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>2.079979756986515</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1927440353367511</v>
+      </c>
       <c r="I23" t="n">
-        <v>7.601077212119493</v>
+        <v>0.1920690665250119</v>
       </c>
       <c r="J23" t="n">
-        <v>8.706296106422514</v>
+        <v>0.1961470983994572</v>
       </c>
       <c r="K23" t="n">
-        <v>6.264736222362677</v>
+        <v>0.1927986405280745</v>
       </c>
       <c r="L23" t="n">
-        <v>6.179453886562431</v>
+        <v>0.1887988347421667</v>
       </c>
       <c r="M23" t="n">
-        <v>4.73670920483566</v>
+        <v>0.1826378354760273</v>
       </c>
       <c r="N23" t="n">
-        <v>5.223924461186074</v>
+        <v>0.3279104499065175</v>
       </c>
       <c r="O23" t="n">
-        <v>3.727351755401545</v>
+        <v>0.2026015015271423</v>
       </c>
       <c r="P23" t="n">
-        <v>4.715881242130918</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.728838111483227</v>
-      </c>
+        <v>0.2018363067855783</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>4.660714093026481</v>
+        <v>7.60064789482138</v>
       </c>
       <c r="S23" t="n">
-        <v>3.725260844608287</v>
+        <v>8.706128074674274</v>
       </c>
       <c r="T23" t="n">
-        <v>4.232820970744682</v>
+        <v>6.264005171571434</v>
       </c>
       <c r="U23" t="n">
-        <v>3.452745139166483</v>
+        <v>6.180046755060745</v>
       </c>
       <c r="V23" t="n">
-        <v>3.737814979871989</v>
+        <v>4.736107078937078</v>
       </c>
       <c r="W23" t="n">
-        <v>3.491936527454818</v>
+        <v>5.224048515733448</v>
       </c>
       <c r="X23" t="n">
-        <v>3.799550204366802</v>
+        <v>3.727243372506654</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.21197137205372</v>
+        <v>4.716064678588662</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.719540405912106</v>
+        <v>3.728814225235121</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.3043102805372012</v>
+        <v>4.661502581334636</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2072642967161948</v>
+        <v>3.725474183877381</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.1307564018182577</v>
+        <v>4.23294360687068</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.07713466532894102</v>
+        <v>3.453793337918856</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.0665701682134012</v>
+        <v>3.738049167540118</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.05940487659492112</v>
+        <v>3.492049466099266</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.05840601998607588</v>
+        <v>3.799692335190477</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.05348659614334619</v>
+        <v>3.213403016642695</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.0455475654201592</v>
+        <v>3.719762973490027</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9.184757377966237</v>
+        <v>0.3046909564581273</v>
       </c>
       <c r="AK23" t="n">
-        <v>7.2349177664794</v>
+        <v>0.2078866087684899</v>
       </c>
       <c r="AL23" t="n">
-        <v>5.662083753726232</v>
+        <v>0.1306663086282241</v>
       </c>
       <c r="AM23" t="n">
+        <v>0.07666742943937867</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.06626104674535012</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.05942487517423729</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.05750057207953399</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.05325954325159409</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.04661996409942396</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9.183985432319274</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>7.234849069098233</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>5.662345873352642</v>
+      </c>
+      <c r="AV23" t="n">
         <v>4.594622027865542</v>
       </c>
-      <c r="AN23" t="n">
-        <v>4.23952223650962</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>4.028169656150619</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>3.951239747047922</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>3.660718316566077</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>3.620726192063513</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>6.69327587687322</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.157299901105043</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5.400381315901851</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>4.725040307342328</v>
-      </c>
       <c r="AW23" t="n">
-        <v>4.454980864637842</v>
+        <v>4.239156414342729</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.256056369098514</v>
+        <v>4.027171529288988</v>
       </c>
       <c r="AY23" t="n">
-        <v>4.020255326000319</v>
+        <v>3.949404052312328</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.894366417044664</v>
+        <v>3.660805778427538</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.750199555520456</v>
+        <v>3.620237379538881</v>
       </c>
       <c r="BB23" t="n">
+        <v>6.693970165675029</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>6.157621956396377</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.400865817528461</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.725547698693939</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.455739173127998</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>4.256484959508999</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>4.019523276263126</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.895736232020038</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>3.750228203582732</v>
+      </c>
+      <c r="BK23" t="n">
         <v>46.95112240124662</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>45.3367226545174</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>44.8495731365006</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>44.8495731365006</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>44.8495731365006</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>44.8495731365006</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>44.8495731365006</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>44.8495731365006</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>44.8495731365006</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>46.70791097200153</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>44.8305581871163</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>44.01566706717531</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>42.7741929081937</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>42.58523959752895</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>42.44237579539928</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>42.44237579539928</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>42.44237579539928</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>42.44237579539928</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.3118034979226388</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2846935102959519</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.2168606447172522</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.2720405589057877</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.2745780610327602</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.1993498056466572</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.3220817249531728</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.2094153222953259</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.2455231987189443</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>3.213403016642695</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>3.719762973490027</v>
       </c>
     </row>
   </sheetData>
